--- a/data/source/trade.xlsx
+++ b/data/source/trade.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2251622C-402C-445B-AD36-763F2E2E3629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15480" yWindow="-1200" windowWidth="15600" windowHeight="18720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="material_master(optional)" sheetId="1" r:id="rId1"/>
@@ -1628,7 +1628,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1657,29 +1657,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill>
@@ -1881,36 +1864,36 @@
     <sortCondition ref="A1:A58"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FE680477-08AA-4C50-B0E7-35C788FE9C9B}" name="material_id" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{FE680477-08AA-4C50-B0E7-35C788FE9C9B}" name="material_id" dataDxfId="2">
       <calculatedColumnFormula>_xlfn.XLOOKUP(표9[[#This Row],[hsk10]],표2[hsk10],표2[material_id])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{6A1D3365-880C-46EA-A0E9-222C9ECD36B8}" name="hsk10"/>
     <tableColumn id="2" xr3:uid="{6CE3F1F7-BFA1-4740-AD48-075581A0AF65}" name="material_name"/>
-    <tableColumn id="3" xr3:uid="{7EC613D4-F0DE-4753-B6F0-FE8770429B48}" name="material_name_hsk" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{7EC613D4-F0DE-4753-B6F0-FE8770429B48}" name="material_name_hsk" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EA39EC6A-89CE-42AE-B5C3-0F352724DF98}" name="표1" displayName="표1" ref="A1:H716" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EA39EC6A-89CE-42AE-B5C3-0F352724DF98}" name="표1" displayName="표1" ref="A1:H716" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12" tableBorderDxfId="11">
   <autoFilter ref="A1:H716" xr:uid="{EA39EC6A-89CE-42AE-B5C3-0F352724DF98}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H706">
     <sortCondition ref="B1:B706"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D2B32EF4-5D25-4D7B-8C34-B5B80DFA0DB4}" name="year" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{6B2896B4-504A-4825-AC96-5DE54C921232}" name="hsk10" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{920B5602-B1C8-433E-BF4A-791A2033EB91}" name="material_name_hsk" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{5586CBA7-4B53-43E2-88B6-D7FF8A79B269}" name="export" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{D9F493FD-EA5C-49D3-909F-31F6A40FB514}" name="import" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{E49B28C8-C50F-4425-8162-8C052B24E6B9}" name="diff" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{D2B32EF4-5D25-4D7B-8C34-B5B80DFA0DB4}" name="year" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{6B2896B4-504A-4825-AC96-5DE54C921232}" name="hsk10" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{920B5602-B1C8-433E-BF4A-791A2033EB91}" name="material_name_hsk" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{5586CBA7-4B53-43E2-88B6-D7FF8A79B269}" name="export" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{D9F493FD-EA5C-49D3-909F-31F6A40FB514}" name="import" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{E49B28C8-C50F-4425-8162-8C052B24E6B9}" name="diff" dataDxfId="5">
       <calculatedColumnFormula>E2-D2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{B8370475-BABD-41C1-92E4-F7887A72CD15}" name="export/import" dataDxfId="5">
+    <tableColumn id="7" xr3:uid="{B8370475-BABD-41C1-92E4-F7887A72CD15}" name="export/import" dataDxfId="4">
       <calculatedColumnFormula>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{FD256F32-F086-4BE5-9BBD-779A9433FC38}" name="balance_index" dataDxfId="4">
+    <tableColumn id="8" xr3:uid="{FD256F32-F086-4BE5-9BBD-779A9433FC38}" name="balance_index" dataDxfId="3">
       <calculatedColumnFormula>ABS(표1[[#This Row],[export]]-표1[[#This Row],[import]])/(표1[[#This Row],[export]]+표1[[#This Row],[import]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5650,7 +5633,7 @@
         <v>117823.8</v>
       </c>
       <c r="F2" s="7">
-        <f>E2-D2</f>
+        <f t="shared" ref="F2:F65" si="0">E2-D2</f>
         <v>117363.2</v>
       </c>
       <c r="G2" t="str">
@@ -5679,7 +5662,7 @@
         <v>163117.5</v>
       </c>
       <c r="F3" s="7">
-        <f>E3-D3</f>
+        <f t="shared" si="0"/>
         <v>161130.29999999999</v>
       </c>
       <c r="G3" t="str">
@@ -5708,7 +5691,7 @@
         <v>209749.1</v>
       </c>
       <c r="F4" s="7">
-        <f>E4-D4</f>
+        <f t="shared" si="0"/>
         <v>209600</v>
       </c>
       <c r="G4" t="str">
@@ -5737,7 +5720,7 @@
         <v>218912.7</v>
       </c>
       <c r="F5" s="7">
-        <f>E5-D5</f>
+        <f t="shared" si="0"/>
         <v>218690.2</v>
       </c>
       <c r="G5" t="str">
@@ -5766,7 +5749,7 @@
         <v>306269.40000000002</v>
       </c>
       <c r="F6" s="7">
-        <f>E6-D6</f>
+        <f t="shared" si="0"/>
         <v>277014.90000000002</v>
       </c>
       <c r="G6" t="str">
@@ -5795,7 +5778,7 @@
         <v>246133.8</v>
       </c>
       <c r="F7" s="7">
-        <f>E7-D7</f>
+        <f t="shared" si="0"/>
         <v>221570.4</v>
       </c>
       <c r="G7" t="str">
@@ -5824,7 +5807,7 @@
         <v>247954.5</v>
       </c>
       <c r="F8" s="7">
-        <f>E8-D8</f>
+        <f t="shared" si="0"/>
         <v>226442.1</v>
       </c>
       <c r="G8" t="str">
@@ -5853,7 +5836,7 @@
         <v>183910.2</v>
       </c>
       <c r="F9" s="7">
-        <f>E9-D9</f>
+        <f t="shared" si="0"/>
         <v>167971.80000000002</v>
       </c>
       <c r="G9" t="str">
@@ -5882,7 +5865,7 @@
         <v>199037.9</v>
       </c>
       <c r="F10" s="7">
-        <f>E10-D10</f>
+        <f t="shared" si="0"/>
         <v>197496.3</v>
       </c>
       <c r="G10" t="str">
@@ -5911,7 +5894,7 @@
         <v>179893.3</v>
       </c>
       <c r="F11" s="7">
-        <f>E11-D11</f>
+        <f t="shared" si="0"/>
         <v>178234.8</v>
       </c>
       <c r="G11" t="str">
@@ -5940,7 +5923,7 @@
         <v>3403.1</v>
       </c>
       <c r="F12" s="10">
-        <f>E12-D12</f>
+        <f t="shared" si="0"/>
         <v>3046.9</v>
       </c>
       <c r="G12" t="str">
@@ -5969,7 +5952,7 @@
         <v>3356.5</v>
       </c>
       <c r="F13" s="10">
-        <f>E13-D13</f>
+        <f t="shared" si="0"/>
         <v>2965.4</v>
       </c>
       <c r="G13" t="str">
@@ -5998,7 +5981,7 @@
         <v>234904.7</v>
       </c>
       <c r="F14" s="10">
-        <f>E14-D14</f>
+        <f t="shared" si="0"/>
         <v>234542.1</v>
       </c>
       <c r="G14" t="str">
@@ -6027,7 +6010,7 @@
         <v>330366.5</v>
       </c>
       <c r="F15" s="10">
-        <f>E15-D15</f>
+        <f t="shared" si="0"/>
         <v>330072.2</v>
       </c>
       <c r="G15" t="str">
@@ -6056,7 +6039,7 @@
         <v>509872.1</v>
       </c>
       <c r="F16" s="10">
-        <f>E16-D16</f>
+        <f t="shared" si="0"/>
         <v>509458.1</v>
       </c>
       <c r="G16" t="str">
@@ -6085,7 +6068,7 @@
         <v>80406.3</v>
       </c>
       <c r="F17" s="10">
-        <f>E17-D17</f>
+        <f t="shared" si="0"/>
         <v>80029.400000000009</v>
       </c>
       <c r="G17" t="str">
@@ -6114,7 +6097,7 @@
         <v>120645</v>
       </c>
       <c r="F18" s="10">
-        <f>E18-D18</f>
+        <f t="shared" si="0"/>
         <v>120317.9</v>
       </c>
       <c r="G18" t="str">
@@ -6143,7 +6126,7 @@
         <v>66295.399999999994</v>
       </c>
       <c r="F19" s="10">
-        <f>E19-D19</f>
+        <f t="shared" si="0"/>
         <v>65873.5</v>
       </c>
       <c r="G19" t="str">
@@ -6172,7 +6155,7 @@
         <v>218942</v>
       </c>
       <c r="F20" s="10">
-        <f>E20-D20</f>
+        <f t="shared" si="0"/>
         <v>218446.5</v>
       </c>
       <c r="G20" t="str">
@@ -6201,7 +6184,7 @@
         <v>404147.5</v>
       </c>
       <c r="F21" s="10">
-        <f>E21-D21</f>
+        <f t="shared" si="0"/>
         <v>403715.9</v>
       </c>
       <c r="G21" t="str">
@@ -6230,7 +6213,7 @@
         <v>146512.79999999999</v>
       </c>
       <c r="F22" s="10">
-        <f>E22-D22</f>
+        <f t="shared" si="0"/>
         <v>-606508.30000000005</v>
       </c>
       <c r="G22" t="str">
@@ -6259,7 +6242,7 @@
         <v>109420.9</v>
       </c>
       <c r="F23" s="10">
-        <f>E23-D23</f>
+        <f t="shared" si="0"/>
         <v>-706218.1</v>
       </c>
       <c r="G23" t="str">
@@ -6288,7 +6271,7 @@
         <v>133347.9</v>
       </c>
       <c r="F24" s="10">
-        <f>E24-D24</f>
+        <f t="shared" si="0"/>
         <v>-690486.5</v>
       </c>
       <c r="G24" t="str">
@@ -6317,7 +6300,7 @@
         <v>108899.8</v>
       </c>
       <c r="F25" s="10">
-        <f>E25-D25</f>
+        <f t="shared" si="0"/>
         <v>-982231.2</v>
       </c>
       <c r="G25" t="str">
@@ -6346,7 +6329,7 @@
         <v>283397.8</v>
       </c>
       <c r="F26" s="10">
-        <f>E26-D26</f>
+        <f t="shared" si="0"/>
         <v>-565041</v>
       </c>
       <c r="G26" t="str">
@@ -6375,7 +6358,7 @@
         <v>207106.7</v>
       </c>
       <c r="F27" s="10">
-        <f>E27-D27</f>
+        <f t="shared" si="0"/>
         <v>-968242.5</v>
       </c>
       <c r="G27" t="str">
@@ -6404,7 +6387,7 @@
         <v>141518.29999999999</v>
       </c>
       <c r="F28" s="10">
-        <f>E28-D28</f>
+        <f t="shared" si="0"/>
         <v>-1445175.2</v>
       </c>
       <c r="G28" t="str">
@@ -6433,7 +6416,7 @@
         <v>162452.79999999999</v>
       </c>
       <c r="F29" s="10">
-        <f>E29-D29</f>
+        <f t="shared" si="0"/>
         <v>-952558.2</v>
       </c>
       <c r="G29" t="str">
@@ -6462,7 +6445,7 @@
         <v>71196.399999999994</v>
       </c>
       <c r="F30" s="10">
-        <f>E30-D30</f>
+        <f t="shared" si="0"/>
         <v>-1777893.4000000001</v>
       </c>
       <c r="G30" t="str">
@@ -6491,7 +6474,7 @@
         <v>21711.5</v>
       </c>
       <c r="F31" s="10">
-        <f>E31-D31</f>
+        <f t="shared" si="0"/>
         <v>-2033178.3</v>
       </c>
       <c r="G31" t="str">
@@ -6520,7 +6503,7 @@
         <v>265495.90000000002</v>
       </c>
       <c r="F32" s="10">
-        <f>E32-D32</f>
+        <f t="shared" si="0"/>
         <v>-1424912</v>
       </c>
       <c r="G32" t="str">
@@ -6549,7 +6532,7 @@
         <v>197871.1</v>
       </c>
       <c r="F33" s="10">
-        <f>E33-D33</f>
+        <f t="shared" si="0"/>
         <v>-1517090</v>
       </c>
       <c r="G33" t="str">
@@ -6578,7 +6561,7 @@
         <v>112785.9</v>
       </c>
       <c r="F34" s="10">
-        <f>E34-D34</f>
+        <f t="shared" si="0"/>
         <v>-1561534.2000000002</v>
       </c>
       <c r="G34" t="str">
@@ -6607,7 +6590,7 @@
         <v>132058.1</v>
       </c>
       <c r="F35" s="10">
-        <f>E35-D35</f>
+        <f t="shared" si="0"/>
         <v>-1524463.5</v>
       </c>
       <c r="G35" t="str">
@@ -6636,7 +6619,7 @@
         <v>124480.2</v>
       </c>
       <c r="F36" s="10">
-        <f>E36-D36</f>
+        <f t="shared" si="0"/>
         <v>-1381601.8</v>
       </c>
       <c r="G36" t="str">
@@ -6665,7 +6648,7 @@
         <v>104682.9</v>
       </c>
       <c r="F37" s="10">
-        <f>E37-D37</f>
+        <f t="shared" si="0"/>
         <v>-1548737.3</v>
       </c>
       <c r="G37" t="str">
@@ -6694,7 +6677,7 @@
         <v>94624.6</v>
       </c>
       <c r="F38" s="10">
-        <f>E38-D38</f>
+        <f t="shared" si="0"/>
         <v>-1538712.7999999998</v>
       </c>
       <c r="G38" t="str">
@@ -6723,7 +6706,7 @@
         <v>112398.5</v>
       </c>
       <c r="F39" s="10">
-        <f>E39-D39</f>
+        <f t="shared" si="0"/>
         <v>-1476578.8</v>
       </c>
       <c r="G39" t="str">
@@ -6752,7 +6735,7 @@
         <v>126732.6</v>
       </c>
       <c r="F40" s="10">
-        <f>E40-D40</f>
+        <f t="shared" si="0"/>
         <v>-1622158.2</v>
       </c>
       <c r="G40" t="str">
@@ -6781,7 +6764,7 @@
         <v>330308</v>
       </c>
       <c r="F41" s="10">
-        <f>E41-D41</f>
+        <f t="shared" si="0"/>
         <v>-1309898.3</v>
       </c>
       <c r="G41" t="str">
@@ -6810,7 +6793,7 @@
         <v>409919.1</v>
       </c>
       <c r="F42" s="10">
-        <f>E42-D42</f>
+        <f t="shared" si="0"/>
         <v>254402.39999999997</v>
       </c>
       <c r="G42" t="str">
@@ -6839,7 +6822,7 @@
         <v>424269.4</v>
       </c>
       <c r="F43" s="10">
-        <f>E43-D43</f>
+        <f t="shared" si="0"/>
         <v>266547.40000000002</v>
       </c>
       <c r="G43" t="str">
@@ -6868,7 +6851,7 @@
         <v>419972.5</v>
       </c>
       <c r="F44" s="10">
-        <f>E44-D44</f>
+        <f t="shared" si="0"/>
         <v>270646.40000000002</v>
       </c>
       <c r="G44" t="str">
@@ -6897,7 +6880,7 @@
         <v>406249.1</v>
       </c>
       <c r="F45" s="10">
-        <f>E45-D45</f>
+        <f t="shared" si="0"/>
         <v>307981</v>
       </c>
       <c r="G45" t="str">
@@ -6926,7 +6909,7 @@
         <v>474368.4</v>
       </c>
       <c r="F46" s="10">
-        <f>E46-D46</f>
+        <f t="shared" si="0"/>
         <v>381947.30000000005</v>
       </c>
       <c r="G46" t="str">
@@ -6955,7 +6938,7 @@
         <v>337394</v>
       </c>
       <c r="F47" s="10">
-        <f>E47-D47</f>
+        <f t="shared" si="0"/>
         <v>212625.3</v>
       </c>
       <c r="G47" t="str">
@@ -6984,7 +6967,7 @@
         <v>205716.5</v>
       </c>
       <c r="F48" s="10">
-        <f>E48-D48</f>
+        <f t="shared" si="0"/>
         <v>24973.399999999994</v>
       </c>
       <c r="G48" t="str">
@@ -7013,7 +6996,7 @@
         <v>312940.79999999999</v>
       </c>
       <c r="F49" s="10">
-        <f>E49-D49</f>
+        <f t="shared" si="0"/>
         <v>144409.4</v>
       </c>
       <c r="G49" t="str">
@@ -7042,7 +7025,7 @@
         <v>345680.9</v>
       </c>
       <c r="F50" s="10">
-        <f>E50-D50</f>
+        <f t="shared" si="0"/>
         <v>97372.400000000023</v>
       </c>
       <c r="G50" t="str">
@@ -7071,7 +7054,7 @@
         <v>354919.9</v>
       </c>
       <c r="F51" s="10">
-        <f>E51-D51</f>
+        <f t="shared" si="0"/>
         <v>130671.40000000002</v>
       </c>
       <c r="G51" t="str">
@@ -7100,7 +7083,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="F52" s="10">
-        <f>E52-D52</f>
+        <f t="shared" si="0"/>
         <v>-13235.699999999999</v>
       </c>
       <c r="G52" t="str">
@@ -7129,7 +7112,7 @@
         <v>0.1</v>
       </c>
       <c r="F53" s="10">
-        <f>E53-D53</f>
+        <f t="shared" si="0"/>
         <v>-53752</v>
       </c>
       <c r="G53" t="str">
@@ -7158,7 +7141,7 @@
         <v>2.1</v>
       </c>
       <c r="F54" s="10">
-        <f>E54-D54</f>
+        <f t="shared" si="0"/>
         <v>-57649.1</v>
       </c>
       <c r="G54" t="str">
@@ -7187,7 +7170,7 @@
         <v>0.1</v>
       </c>
       <c r="F55" s="10">
-        <f>E55-D55</f>
+        <f t="shared" si="0"/>
         <v>-58198.200000000004</v>
       </c>
       <c r="G55" t="str">
@@ -7216,7 +7199,7 @@
         <v>0.1</v>
       </c>
       <c r="F56" s="10">
-        <f>E56-D56</f>
+        <f t="shared" si="0"/>
         <v>-57908.6</v>
       </c>
       <c r="G56" t="str">
@@ -7245,7 +7228,7 @@
         <v>0.1</v>
       </c>
       <c r="F57" s="10">
-        <f>E57-D57</f>
+        <f t="shared" si="0"/>
         <v>-68626</v>
       </c>
       <c r="G57" t="str">
@@ -7274,7 +7257,7 @@
         <v>0.1</v>
       </c>
       <c r="F58" s="10">
-        <f>E58-D58</f>
+        <f t="shared" si="0"/>
         <v>-61490.9</v>
       </c>
       <c r="G58" t="str">
@@ -7303,7 +7286,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="10">
-        <f>E59-D59</f>
+        <f t="shared" si="0"/>
         <v>-37508</v>
       </c>
       <c r="G59" t="str">
@@ -7332,7 +7315,7 @@
         <v>0.1</v>
       </c>
       <c r="F60" s="10">
-        <f>E60-D60</f>
+        <f t="shared" si="0"/>
         <v>-62257.4</v>
       </c>
       <c r="G60" t="str">
@@ -7361,7 +7344,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="10">
-        <f>E61-D61</f>
+        <f t="shared" si="0"/>
         <v>-54625.7</v>
       </c>
       <c r="G61" t="str">
@@ -7390,7 +7373,7 @@
         <v>22121.599999999999</v>
       </c>
       <c r="F62" s="7">
-        <f>E62-D62</f>
+        <f t="shared" si="0"/>
         <v>22066.799999999999</v>
       </c>
       <c r="G62" t="str">
@@ -7419,7 +7402,7 @@
         <v>23581.4</v>
       </c>
       <c r="F63" s="7">
-        <f>E63-D63</f>
+        <f t="shared" si="0"/>
         <v>22771.600000000002</v>
       </c>
       <c r="G63" t="str">
@@ -7448,7 +7431,7 @@
         <v>21331</v>
       </c>
       <c r="F64" s="7">
-        <f>E64-D64</f>
+        <f t="shared" si="0"/>
         <v>21240.5</v>
       </c>
       <c r="G64" t="str">
@@ -7477,7 +7460,7 @@
         <v>25235</v>
       </c>
       <c r="F65" s="7">
-        <f>E65-D65</f>
+        <f t="shared" si="0"/>
         <v>24877.599999999999</v>
       </c>
       <c r="G65" t="str">
@@ -7506,7 +7489,7 @@
         <v>24759.4</v>
       </c>
       <c r="F66" s="7">
-        <f>E66-D66</f>
+        <f t="shared" ref="F66:F129" si="1">E66-D66</f>
         <v>24507.200000000001</v>
       </c>
       <c r="G66" t="str">
@@ -7535,7 +7518,7 @@
         <v>56025.5</v>
       </c>
       <c r="F67" s="7">
-        <f>E67-D67</f>
+        <f t="shared" si="1"/>
         <v>55672</v>
       </c>
       <c r="G67" t="str">
@@ -7564,7 +7547,7 @@
         <v>60866.5</v>
       </c>
       <c r="F68" s="7">
-        <f>E68-D68</f>
+        <f t="shared" si="1"/>
         <v>60866.400000000001</v>
       </c>
       <c r="G68" t="str">
@@ -7593,7 +7576,7 @@
         <v>38050</v>
       </c>
       <c r="F69" s="7">
-        <f>E69-D69</f>
+        <f t="shared" si="1"/>
         <v>38034.9</v>
       </c>
       <c r="G69" t="str">
@@ -7622,7 +7605,7 @@
         <v>38477.699999999997</v>
       </c>
       <c r="F70" s="7">
-        <f>E70-D70</f>
+        <f t="shared" si="1"/>
         <v>38368.5</v>
       </c>
       <c r="G70" t="str">
@@ -7651,7 +7634,7 @@
         <v>30211.8</v>
       </c>
       <c r="F71" s="7">
-        <f>E71-D71</f>
+        <f t="shared" si="1"/>
         <v>30191.5</v>
       </c>
       <c r="G71" t="str">
@@ -7680,7 +7663,7 @@
         <v>59681.599999999999</v>
       </c>
       <c r="F72" s="7">
-        <f>E72-D72</f>
+        <f t="shared" si="1"/>
         <v>59681.599999999999</v>
       </c>
       <c r="G72" t="str">
@@ -7709,7 +7692,7 @@
         <v>68026.100000000006</v>
       </c>
       <c r="F73" s="7">
-        <f>E73-D73</f>
+        <f t="shared" si="1"/>
         <v>68014.900000000009</v>
       </c>
       <c r="G73" t="str">
@@ -7738,7 +7721,7 @@
         <v>64239.1</v>
       </c>
       <c r="F74" s="7">
-        <f>E74-D74</f>
+        <f t="shared" si="1"/>
         <v>64239.1</v>
       </c>
       <c r="G74" t="str">
@@ -7767,7 +7750,7 @@
         <v>101336.8</v>
       </c>
       <c r="F75" s="7">
-        <f>E75-D75</f>
+        <f t="shared" si="1"/>
         <v>101312.8</v>
       </c>
       <c r="G75" t="str">
@@ -7796,7 +7779,7 @@
         <v>89540.7</v>
       </c>
       <c r="F76" s="7">
-        <f>E76-D76</f>
+        <f t="shared" si="1"/>
         <v>89442.599999999991</v>
       </c>
       <c r="G76" t="str">
@@ -7825,7 +7808,7 @@
         <v>87481.9</v>
       </c>
       <c r="F77" s="7">
-        <f>E77-D77</f>
+        <f t="shared" si="1"/>
         <v>87358</v>
       </c>
       <c r="G77" t="str">
@@ -7854,7 +7837,7 @@
         <v>111144.3</v>
       </c>
       <c r="F78" s="7">
-        <f>E78-D78</f>
+        <f t="shared" si="1"/>
         <v>110996.8</v>
       </c>
       <c r="G78" t="str">
@@ -7883,7 +7866,7 @@
         <v>98415.8</v>
       </c>
       <c r="F79" s="7">
-        <f>E79-D79</f>
+        <f t="shared" si="1"/>
         <v>98086.1</v>
       </c>
       <c r="G79" t="str">
@@ -7912,7 +7895,7 @@
         <v>93935.5</v>
       </c>
       <c r="F80" s="7">
-        <f>E80-D80</f>
+        <f t="shared" si="1"/>
         <v>93474.8</v>
       </c>
       <c r="G80" t="str">
@@ -7941,7 +7924,7 @@
         <v>100621.1</v>
       </c>
       <c r="F81" s="7">
-        <f>E81-D81</f>
+        <f t="shared" si="1"/>
         <v>100302.40000000001</v>
       </c>
       <c r="G81" t="str">
@@ -7970,7 +7953,7 @@
         <v>23710.1</v>
       </c>
       <c r="F82" s="7">
-        <f>E82-D82</f>
+        <f t="shared" si="1"/>
         <v>18136.899999999998</v>
       </c>
       <c r="G82" t="str">
@@ -7999,7 +7982,7 @@
         <v>40981.1</v>
       </c>
       <c r="F83" s="7">
-        <f>E83-D83</f>
+        <f t="shared" si="1"/>
         <v>35302</v>
       </c>
       <c r="G83" t="str">
@@ -8028,7 +8011,7 @@
         <v>72900.5</v>
       </c>
       <c r="F84" s="7">
-        <f>E84-D84</f>
+        <f t="shared" si="1"/>
         <v>68243.399999999994</v>
       </c>
       <c r="G84" t="str">
@@ -8057,7 +8040,7 @@
         <v>47886.6</v>
       </c>
       <c r="F85" s="7">
-        <f>E85-D85</f>
+        <f t="shared" si="1"/>
         <v>40037.199999999997</v>
       </c>
       <c r="G85" t="str">
@@ -8086,7 +8069,7 @@
         <v>12540</v>
       </c>
       <c r="F86" s="7">
-        <f>E86-D86</f>
+        <f t="shared" si="1"/>
         <v>8211.2000000000007</v>
       </c>
       <c r="G86" t="str">
@@ -8115,7 +8098,7 @@
         <v>36395.800000000003</v>
       </c>
       <c r="F87" s="7">
-        <f>E87-D87</f>
+        <f t="shared" si="1"/>
         <v>33868.5</v>
       </c>
       <c r="G87" t="str">
@@ -8144,7 +8127,7 @@
         <v>21040.5</v>
       </c>
       <c r="F88" s="7">
-        <f>E88-D88</f>
+        <f t="shared" si="1"/>
         <v>15468.6</v>
       </c>
       <c r="G88" t="str">
@@ -8173,7 +8156,7 @@
         <v>3283</v>
       </c>
       <c r="F89" s="7">
-        <f>E89-D89</f>
+        <f t="shared" si="1"/>
         <v>2550.5</v>
       </c>
       <c r="G89" t="str">
@@ -8202,7 +8185,7 @@
         <v>6204.7</v>
       </c>
       <c r="F90" s="7">
-        <f>E90-D90</f>
+        <f t="shared" si="1"/>
         <v>5741.8</v>
       </c>
       <c r="G90" t="str">
@@ -8231,7 +8214,7 @@
         <v>5154.3</v>
       </c>
       <c r="F91" s="7">
-        <f>E91-D91</f>
+        <f t="shared" si="1"/>
         <v>4505.9000000000005</v>
       </c>
       <c r="G91" t="str">
@@ -8260,7 +8243,7 @@
         <v>31277.7</v>
       </c>
       <c r="F92" s="7">
-        <f>E92-D92</f>
+        <f t="shared" si="1"/>
         <v>-2013492</v>
       </c>
       <c r="G92" t="str">
@@ -8289,7 +8272,7 @@
         <v>18002.7</v>
       </c>
       <c r="F93" s="7">
-        <f>E93-D93</f>
+        <f t="shared" si="1"/>
         <v>-2613917.2999999998</v>
       </c>
       <c r="G93" t="str">
@@ -8318,7 +8301,7 @@
         <v>41601.9</v>
       </c>
       <c r="F94" s="7">
-        <f>E94-D94</f>
+        <f t="shared" si="1"/>
         <v>-2527929.9</v>
       </c>
       <c r="G94" t="str">
@@ -8347,7 +8330,7 @@
         <v>23452.9</v>
       </c>
       <c r="F95" s="7">
-        <f>E95-D95</f>
+        <f t="shared" si="1"/>
         <v>-2603907.1</v>
       </c>
       <c r="G95" t="str">
@@ -8376,7 +8359,7 @@
         <v>58441.5</v>
       </c>
       <c r="F96" s="7">
-        <f>E96-D96</f>
+        <f t="shared" si="1"/>
         <v>-2161873.7999999998</v>
       </c>
       <c r="G96" t="str">
@@ -8405,7 +8388,7 @@
         <v>35603.1</v>
       </c>
       <c r="F97" s="7">
-        <f>E97-D97</f>
+        <f t="shared" si="1"/>
         <v>-2441545.4</v>
       </c>
       <c r="G97" t="str">
@@ -8434,7 +8417,7 @@
         <v>62920.6</v>
       </c>
       <c r="F98" s="7">
-        <f>E98-D98</f>
+        <f t="shared" si="1"/>
         <v>-2505688.1</v>
       </c>
       <c r="G98" t="str">
@@ -8463,7 +8446,7 @@
         <v>66138.899999999994</v>
       </c>
       <c r="F99" s="7">
-        <f>E99-D99</f>
+        <f t="shared" si="1"/>
         <v>-2853486.8000000003</v>
       </c>
       <c r="G99" t="str">
@@ -8492,7 +8475,7 @@
         <v>88857.3</v>
       </c>
       <c r="F100" s="7">
-        <f>E100-D100</f>
+        <f t="shared" si="1"/>
         <v>-2944494.5</v>
       </c>
       <c r="G100" t="str">
@@ -8521,7 +8504,7 @@
         <v>97976.2</v>
       </c>
       <c r="F101" s="7">
-        <f>E101-D101</f>
+        <f t="shared" si="1"/>
         <v>-2928375.5999999996</v>
       </c>
       <c r="G101" t="str">
@@ -8550,7 +8533,7 @@
         <v>525757.30000000005</v>
       </c>
       <c r="F102" s="7">
-        <f>E102-D102</f>
+        <f t="shared" si="1"/>
         <v>-6820.1999999999534</v>
       </c>
       <c r="G102" t="str">
@@ -8579,7 +8562,7 @@
         <v>736086.3</v>
       </c>
       <c r="F103" s="7">
-        <f>E103-D103</f>
+        <f t="shared" si="1"/>
         <v>375310.00000000006</v>
       </c>
       <c r="G103" t="str">
@@ -8608,7 +8591,7 @@
         <v>812442.6</v>
       </c>
       <c r="F104" s="7">
-        <f>E104-D104</f>
+        <f t="shared" si="1"/>
         <v>458085.5</v>
       </c>
       <c r="G104" t="str">
@@ -8637,7 +8620,7 @@
         <v>630015.4</v>
       </c>
       <c r="F105" s="7">
-        <f>E105-D105</f>
+        <f t="shared" si="1"/>
         <v>169740</v>
       </c>
       <c r="G105" t="str">
@@ -8666,7 +8649,7 @@
         <v>418808.3</v>
       </c>
       <c r="F106" s="7">
-        <f>E106-D106</f>
+        <f t="shared" si="1"/>
         <v>-9770</v>
       </c>
       <c r="G106" t="str">
@@ -8695,7 +8678,7 @@
         <v>590298.30000000005</v>
       </c>
       <c r="F107" s="7">
-        <f>E107-D107</f>
+        <f t="shared" si="1"/>
         <v>317840.30000000005</v>
       </c>
       <c r="G107" t="str">
@@ -8724,7 +8707,7 @@
         <v>603465.4</v>
       </c>
       <c r="F108" s="7">
-        <f>E108-D108</f>
+        <f t="shared" si="1"/>
         <v>99316</v>
       </c>
       <c r="G108" t="str">
@@ -8753,7 +8736,7 @@
         <v>425103.2</v>
       </c>
       <c r="F109" s="7">
-        <f>E109-D109</f>
+        <f t="shared" si="1"/>
         <v>-393864.3</v>
       </c>
       <c r="G109" t="str">
@@ -8782,7 +8765,7 @@
         <v>452736.5</v>
       </c>
       <c r="F110" s="7">
-        <f>E110-D110</f>
+        <f t="shared" si="1"/>
         <v>-138472.40000000002</v>
       </c>
       <c r="G110" t="str">
@@ -8811,7 +8794,7 @@
         <v>610278</v>
       </c>
       <c r="F111" s="7">
-        <f>E111-D111</f>
+        <f t="shared" si="1"/>
         <v>74557.599999999977</v>
       </c>
       <c r="G111" t="str">
@@ -8840,7 +8823,7 @@
         <v>52699.7</v>
       </c>
       <c r="F112" s="7">
-        <f>E112-D112</f>
+        <f t="shared" si="1"/>
         <v>46017.1</v>
       </c>
       <c r="G112" t="str">
@@ -8869,7 +8852,7 @@
         <v>28122.5</v>
       </c>
       <c r="F113" s="7">
-        <f>E113-D113</f>
+        <f t="shared" si="1"/>
         <v>-20309.900000000001</v>
       </c>
       <c r="G113" t="str">
@@ -8898,7 +8881,7 @@
         <v>10340.700000000001</v>
       </c>
       <c r="F114" s="7">
-        <f>E114-D114</f>
+        <f t="shared" si="1"/>
         <v>-6985.7000000000007</v>
       </c>
       <c r="G114" t="str">
@@ -8927,7 +8910,7 @@
         <v>5032.3</v>
       </c>
       <c r="F115" s="7">
-        <f>E115-D115</f>
+        <f t="shared" si="1"/>
         <v>-66004.5</v>
       </c>
       <c r="G115" t="str">
@@ -8956,7 +8939,7 @@
         <v>9057.2999999999993</v>
       </c>
       <c r="F116" s="7">
-        <f>E116-D116</f>
+        <f t="shared" si="1"/>
         <v>-46917.3</v>
       </c>
       <c r="G116" t="str">
@@ -8985,7 +8968,7 @@
         <v>9907.1</v>
       </c>
       <c r="F117" s="7">
-        <f>E117-D117</f>
+        <f t="shared" si="1"/>
         <v>-27365.4</v>
       </c>
       <c r="G117" t="str">
@@ -9014,7 +8997,7 @@
         <v>5984.5</v>
       </c>
       <c r="F118" s="7">
-        <f>E118-D118</f>
+        <f t="shared" si="1"/>
         <v>-80308.7</v>
       </c>
       <c r="G118" t="str">
@@ -9043,7 +9026,7 @@
         <v>20819.599999999999</v>
       </c>
       <c r="F119" s="7">
-        <f>E119-D119</f>
+        <f t="shared" si="1"/>
         <v>-96069.4</v>
       </c>
       <c r="G119" t="str">
@@ -9072,7 +9055,7 @@
         <v>7779.2</v>
       </c>
       <c r="F120" s="7">
-        <f>E120-D120</f>
+        <f t="shared" si="1"/>
         <v>-79686</v>
       </c>
       <c r="G120" t="str">
@@ -9101,7 +9084,7 @@
         <v>3918.1</v>
       </c>
       <c r="F121" s="7">
-        <f>E121-D121</f>
+        <f t="shared" si="1"/>
         <v>-87075.199999999997</v>
       </c>
       <c r="G121" t="str">
@@ -9130,7 +9113,7 @@
         <v>47128.7</v>
       </c>
       <c r="F122" s="7">
-        <f>E122-D122</f>
+        <f t="shared" si="1"/>
         <v>47128.7</v>
       </c>
       <c r="G122" t="str">
@@ -9159,7 +9142,7 @@
         <v>87975.7</v>
       </c>
       <c r="F123" s="7">
-        <f>E123-D123</f>
+        <f t="shared" si="1"/>
         <v>87975.7</v>
       </c>
       <c r="G123" t="str">
@@ -9188,7 +9171,7 @@
         <v>80009.8</v>
       </c>
       <c r="F124" s="7">
-        <f>E124-D124</f>
+        <f t="shared" si="1"/>
         <v>80009.600000000006</v>
       </c>
       <c r="G124" t="str">
@@ -9217,7 +9200,7 @@
         <v>67839</v>
       </c>
       <c r="F125" s="7">
-        <f>E125-D125</f>
+        <f t="shared" si="1"/>
         <v>64057.7</v>
       </c>
       <c r="G125" t="str">
@@ -9246,7 +9229,7 @@
         <v>33301.699999999997</v>
       </c>
       <c r="F126" s="7">
-        <f>E126-D126</f>
+        <f t="shared" si="1"/>
         <v>24361.999999999996</v>
       </c>
       <c r="G126" t="str">
@@ -9275,7 +9258,7 @@
         <v>22698.1</v>
       </c>
       <c r="F127" s="7">
-        <f>E127-D127</f>
+        <f t="shared" si="1"/>
         <v>5392.1999999999971</v>
       </c>
       <c r="G127" t="str">
@@ -9304,7 +9287,7 @@
         <v>13580.7</v>
       </c>
       <c r="F128" s="7">
-        <f>E128-D128</f>
+        <f t="shared" si="1"/>
         <v>6735.5000000000009</v>
       </c>
       <c r="G128" t="str">
@@ -9333,7 +9316,7 @@
         <v>20604.8</v>
       </c>
       <c r="F129" s="7">
-        <f>E129-D129</f>
+        <f t="shared" si="1"/>
         <v>16409.3</v>
       </c>
       <c r="G129" t="str">
@@ -9362,7 +9345,7 @@
         <v>14425.7</v>
       </c>
       <c r="F130" s="7">
-        <f>E130-D130</f>
+        <f t="shared" ref="F130:F193" si="2">E130-D130</f>
         <v>14425.7</v>
       </c>
       <c r="G130" t="str">
@@ -9391,7 +9374,7 @@
         <v>0.1</v>
       </c>
       <c r="F131" s="7">
-        <f>E131-D131</f>
+        <f t="shared" si="2"/>
         <v>-119.9</v>
       </c>
       <c r="G131" t="str">
@@ -9420,7 +9403,7 @@
         <v>43589.7</v>
       </c>
       <c r="F132" s="7">
-        <f>E132-D132</f>
+        <f t="shared" si="2"/>
         <v>-6391022.5</v>
       </c>
       <c r="G132" t="str">
@@ -9449,7 +9432,7 @@
         <v>24764.2</v>
       </c>
       <c r="F133" s="7">
-        <f>E133-D133</f>
+        <f t="shared" si="2"/>
         <v>-7290588.8999999994</v>
       </c>
       <c r="G133" t="str">
@@ -9478,7 +9461,7 @@
         <v>24511.599999999999</v>
       </c>
       <c r="F134" s="7">
-        <f>E134-D134</f>
+        <f t="shared" si="2"/>
         <v>-7359003.1000000006</v>
       </c>
       <c r="G134" t="str">
@@ -9507,7 +9490,7 @@
         <v>20001.7</v>
       </c>
       <c r="F135" s="7">
-        <f>E135-D135</f>
+        <f t="shared" si="2"/>
         <v>-7012495.7000000002</v>
       </c>
       <c r="G135" t="str">
@@ -9536,7 +9519,7 @@
         <v>10003</v>
       </c>
       <c r="F136" s="7">
-        <f>E136-D136</f>
+        <f t="shared" si="2"/>
         <v>-6065088.7000000002</v>
       </c>
       <c r="G136" t="str">
@@ -9565,7 +9548,7 @@
         <v>14268.2</v>
       </c>
       <c r="F137" s="7">
-        <f>E137-D137</f>
+        <f t="shared" si="2"/>
         <v>-6162521.7999999998</v>
       </c>
       <c r="G137" t="str">
@@ -9594,7 +9577,7 @@
         <v>29015.8</v>
       </c>
       <c r="F138" s="7">
-        <f>E138-D138</f>
+        <f t="shared" si="2"/>
         <v>-5223774.9000000004</v>
       </c>
       <c r="G138" t="str">
@@ -9623,7 +9606,7 @@
         <v>54223</v>
       </c>
       <c r="F139" s="7">
-        <f>E139-D139</f>
+        <f t="shared" si="2"/>
         <v>-4803053.5999999996</v>
       </c>
       <c r="G139" t="str">
@@ -9652,7 +9635,7 @@
         <v>74178</v>
       </c>
       <c r="F140" s="7">
-        <f>E140-D140</f>
+        <f t="shared" si="2"/>
         <v>-4826576.3</v>
       </c>
       <c r="G140" t="str">
@@ -9681,7 +9664,7 @@
         <v>92301.1</v>
       </c>
       <c r="F141" s="7">
-        <f>E141-D141</f>
+        <f t="shared" si="2"/>
         <v>-4847448.5</v>
       </c>
       <c r="G141" t="str">
@@ -9710,7 +9693,7 @@
         <v>148.5</v>
       </c>
       <c r="F142" s="10">
-        <f>E142-D142</f>
+        <f t="shared" si="2"/>
         <v>-37069.1</v>
       </c>
       <c r="G142" t="str">
@@ -9739,7 +9722,7 @@
         <v>57.6</v>
       </c>
       <c r="F143" s="10">
-        <f>E143-D143</f>
+        <f t="shared" si="2"/>
         <v>-22805.7</v>
       </c>
       <c r="G143" t="str">
@@ -9768,7 +9751,7 @@
         <v>18.600000000000001</v>
       </c>
       <c r="F144" s="10">
-        <f>E144-D144</f>
+        <f t="shared" si="2"/>
         <v>-37491.200000000004</v>
       </c>
       <c r="G144" t="str">
@@ -9797,7 +9780,7 @@
         <v>18.5</v>
       </c>
       <c r="F145" s="10">
-        <f>E145-D145</f>
+        <f t="shared" si="2"/>
         <v>-476.3</v>
       </c>
       <c r="G145" t="str">
@@ -9826,7 +9809,7 @@
         <v>5.9</v>
       </c>
       <c r="F146" s="10">
-        <f>E146-D146</f>
+        <f t="shared" si="2"/>
         <v>-620.4</v>
       </c>
       <c r="G146" t="str">
@@ -9855,7 +9838,7 @@
         <v>5.6</v>
       </c>
       <c r="F147" s="10">
-        <f>E147-D147</f>
+        <f t="shared" si="2"/>
         <v>-608.19999999999993</v>
       </c>
       <c r="G147" t="str">
@@ -9884,7 +9867,7 @@
         <v>7</v>
       </c>
       <c r="F148" s="10">
-        <f>E148-D148</f>
+        <f t="shared" si="2"/>
         <v>-617.79999999999995</v>
       </c>
       <c r="G148" t="str">
@@ -9913,7 +9896,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="F149" s="10">
-        <f>E149-D149</f>
+        <f t="shared" si="2"/>
         <v>-897.3</v>
       </c>
       <c r="G149" t="str">
@@ -9942,7 +9925,7 @@
         <v>5902.7</v>
       </c>
       <c r="F150" s="10">
-        <f>E150-D150</f>
+        <f t="shared" si="2"/>
         <v>5133.3999999999996</v>
       </c>
       <c r="G150" t="str">
@@ -9971,7 +9954,7 @@
         <v>1.6</v>
       </c>
       <c r="F151" s="10">
-        <f>E151-D151</f>
+        <f t="shared" si="2"/>
         <v>-696.1</v>
       </c>
       <c r="G151" t="str">
@@ -10000,7 +9983,7 @@
         <v>806172.5</v>
       </c>
       <c r="F152" s="7">
-        <f>E152-D152</f>
+        <f t="shared" si="2"/>
         <v>-486157</v>
       </c>
       <c r="G152" t="str">
@@ -10029,7 +10012,7 @@
         <v>794030.1</v>
       </c>
       <c r="F153" s="7">
-        <f>E153-D153</f>
+        <f t="shared" si="2"/>
         <v>-467839.00000000012</v>
       </c>
       <c r="G153" t="str">
@@ -10058,7 +10041,7 @@
         <v>305442.2</v>
       </c>
       <c r="F154" s="7">
-        <f>E154-D154</f>
+        <f t="shared" si="2"/>
         <v>-535559.30000000005</v>
       </c>
       <c r="G154" t="str">
@@ -10087,7 +10070,7 @@
         <v>489455.8</v>
       </c>
       <c r="F155" s="7">
-        <f>E155-D155</f>
+        <f t="shared" si="2"/>
         <v>-180243.00000000006</v>
       </c>
       <c r="G155" t="str">
@@ -10116,7 +10099,7 @@
         <v>726653.6</v>
       </c>
       <c r="F156" s="7">
-        <f>E156-D156</f>
+        <f t="shared" si="2"/>
         <v>-38849</v>
       </c>
       <c r="G156" t="str">
@@ -10145,7 +10128,7 @@
         <v>433677.4</v>
       </c>
       <c r="F157" s="7">
-        <f>E157-D157</f>
+        <f t="shared" si="2"/>
         <v>-255433.40000000002</v>
       </c>
       <c r="G157" t="str">
@@ -10174,7 +10157,7 @@
         <v>478635.2</v>
       </c>
       <c r="F158" s="7">
-        <f>E158-D158</f>
+        <f t="shared" si="2"/>
         <v>-79472.999999999942</v>
       </c>
       <c r="G158" t="str">
@@ -10203,7 +10186,7 @@
         <v>774897.6</v>
       </c>
       <c r="F159" s="7">
-        <f>E159-D159</f>
+        <f t="shared" si="2"/>
         <v>477915.39999999997</v>
       </c>
       <c r="G159" t="str">
@@ -10232,7 +10215,7 @@
         <v>586773.6</v>
       </c>
       <c r="F160" s="7">
-        <f>E160-D160</f>
+        <f t="shared" si="2"/>
         <v>285251.89999999997</v>
       </c>
       <c r="G160" t="str">
@@ -10261,7 +10244,7 @@
         <v>581273.9</v>
       </c>
       <c r="F161" s="7">
-        <f>E161-D161</f>
+        <f t="shared" si="2"/>
         <v>300750.90000000002</v>
       </c>
       <c r="G161" t="str">
@@ -10290,7 +10273,7 @@
         <v>1.3</v>
       </c>
       <c r="F162" s="7">
-        <f>E162-D162</f>
+        <f t="shared" si="2"/>
         <v>-16.599999999999998</v>
       </c>
       <c r="G162" t="str">
@@ -10319,7 +10302,7 @@
         <v>2.5</v>
       </c>
       <c r="F163" s="7">
-        <f>E163-D163</f>
+        <f t="shared" si="2"/>
         <v>-33.5</v>
       </c>
       <c r="G163" t="str">
@@ -10348,7 +10331,7 @@
         <v>1.4</v>
       </c>
       <c r="F164" s="7">
-        <f>E164-D164</f>
+        <f t="shared" si="2"/>
         <v>-69.599999999999994</v>
       </c>
       <c r="G164" t="str">
@@ -10377,7 +10360,7 @@
         <v>0.9</v>
       </c>
       <c r="F165" s="7">
-        <f>E165-D165</f>
+        <f t="shared" si="2"/>
         <v>-53</v>
       </c>
       <c r="G165" t="str">
@@ -10406,7 +10389,7 @@
         <v>3.6</v>
       </c>
       <c r="F166" s="7">
-        <f>E166-D166</f>
+        <f t="shared" si="2"/>
         <v>-68.400000000000006</v>
       </c>
       <c r="G166" t="str">
@@ -10435,7 +10418,7 @@
         <v>21.2</v>
       </c>
       <c r="F167" s="7">
-        <f>E167-D167</f>
+        <f t="shared" si="2"/>
         <v>-34.799999999999997</v>
       </c>
       <c r="G167" t="str">
@@ -10464,7 +10447,7 @@
         <v>35.299999999999997</v>
       </c>
       <c r="F168" s="7">
-        <f>E168-D168</f>
+        <f t="shared" si="2"/>
         <v>-17.800000000000004</v>
       </c>
       <c r="G168" t="str">
@@ -10493,7 +10476,7 @@
         <v>17.100000000000001</v>
       </c>
       <c r="F169" s="7">
-        <f>E169-D169</f>
+        <f t="shared" si="2"/>
         <v>-37</v>
       </c>
       <c r="G169" t="str">
@@ -10522,7 +10505,7 @@
         <v>7.6</v>
       </c>
       <c r="F170" s="7">
-        <f>E170-D170</f>
+        <f t="shared" si="2"/>
         <v>-10.4</v>
       </c>
       <c r="G170" t="str">
@@ -10551,7 +10534,7 @@
         <v>21</v>
       </c>
       <c r="F171" s="7">
-        <f>E171-D171</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="G171" t="str">
@@ -10580,7 +10563,7 @@
         <v>34733.5</v>
       </c>
       <c r="F172" s="7">
-        <f>E172-D172</f>
+        <f t="shared" si="2"/>
         <v>33774.400000000001</v>
       </c>
       <c r="G172" t="str">
@@ -10609,7 +10592,7 @@
         <v>16490.900000000001</v>
       </c>
       <c r="F173" s="7">
-        <f>E173-D173</f>
+        <f t="shared" si="2"/>
         <v>8987.0000000000018</v>
       </c>
       <c r="G173" t="str">
@@ -10638,7 +10621,7 @@
         <v>26961.8</v>
       </c>
       <c r="F174" s="7">
-        <f>E174-D174</f>
+        <f t="shared" si="2"/>
         <v>15880.599999999999</v>
       </c>
       <c r="G174" t="str">
@@ -10667,7 +10650,7 @@
         <v>16957.099999999999</v>
       </c>
       <c r="F175" s="7">
-        <f>E175-D175</f>
+        <f t="shared" si="2"/>
         <v>6863.7999999999993</v>
       </c>
       <c r="G175" t="str">
@@ -10696,7 +10679,7 @@
         <v>13017.4</v>
       </c>
       <c r="F176" s="7">
-        <f>E176-D176</f>
+        <f t="shared" si="2"/>
         <v>-16650.400000000001</v>
       </c>
       <c r="G176" t="str">
@@ -10725,7 +10708,7 @@
         <v>25826.2</v>
       </c>
       <c r="F177" s="7">
-        <f>E177-D177</f>
+        <f t="shared" si="2"/>
         <v>-5116.3999999999978</v>
       </c>
       <c r="G177" t="str">
@@ -10754,7 +10737,7 @@
         <v>8134.7</v>
       </c>
       <c r="F178" s="7">
-        <f>E178-D178</f>
+        <f t="shared" si="2"/>
         <v>2356.1999999999998</v>
       </c>
       <c r="G178" t="str">
@@ -10783,7 +10766,7 @@
         <v>9716.7000000000007</v>
       </c>
       <c r="F179" s="7">
-        <f>E179-D179</f>
+        <f t="shared" si="2"/>
         <v>-46821.5</v>
       </c>
       <c r="G179" t="str">
@@ -10812,7 +10795,7 @@
         <v>16849.5</v>
       </c>
       <c r="F180" s="7">
-        <f>E180-D180</f>
+        <f t="shared" si="2"/>
         <v>-86777.7</v>
       </c>
       <c r="G180" t="str">
@@ -10841,7 +10824,7 @@
         <v>8882.1</v>
       </c>
       <c r="F181" s="7">
-        <f>E181-D181</f>
+        <f t="shared" si="2"/>
         <v>-164817.29999999999</v>
       </c>
       <c r="G181" t="str">
@@ -10870,7 +10853,7 @@
         <v>200366.4</v>
       </c>
       <c r="F182" s="7">
-        <f>E182-D182</f>
+        <f t="shared" si="2"/>
         <v>1145.1999999999825</v>
       </c>
       <c r="G182" t="str">
@@ -10899,7 +10882,7 @@
         <v>228287.3</v>
       </c>
       <c r="F183" s="7">
-        <f>E183-D183</f>
+        <f t="shared" si="2"/>
         <v>43918.5</v>
       </c>
       <c r="G183" t="str">
@@ -10928,7 +10911,7 @@
         <v>181851.4</v>
       </c>
       <c r="F184" s="7">
-        <f>E184-D184</f>
+        <f t="shared" si="2"/>
         <v>-81590.600000000006</v>
       </c>
       <c r="G184" t="str">
@@ -10957,7 +10940,7 @@
         <v>159769.1</v>
       </c>
       <c r="F185" s="7">
-        <f>E185-D185</f>
+        <f t="shared" si="2"/>
         <v>-121234.99999999997</v>
       </c>
       <c r="G185" t="str">
@@ -10986,7 +10969,7 @@
         <v>144933.79999999999</v>
       </c>
       <c r="F186" s="7">
-        <f>E186-D186</f>
+        <f t="shared" si="2"/>
         <v>-197917.40000000002</v>
       </c>
       <c r="G186" t="str">
@@ -11015,7 +10998,7 @@
         <v>59237.5</v>
       </c>
       <c r="F187" s="7">
-        <f>E187-D187</f>
+        <f t="shared" si="2"/>
         <v>-163777.79999999999</v>
       </c>
       <c r="G187" t="str">
@@ -11044,7 +11027,7 @@
         <v>34516.400000000001</v>
       </c>
       <c r="F188" s="7">
-        <f>E188-D188</f>
+        <f t="shared" si="2"/>
         <v>-266867.3</v>
       </c>
       <c r="G188" t="str">
@@ -11073,7 +11056,7 @@
         <v>9146</v>
       </c>
       <c r="F189" s="7">
-        <f>E189-D189</f>
+        <f t="shared" si="2"/>
         <v>-296517.8</v>
       </c>
       <c r="G189" t="str">
@@ -11102,7 +11085,7 @@
         <v>26341</v>
       </c>
       <c r="F190" s="7">
-        <f>E190-D190</f>
+        <f t="shared" si="2"/>
         <v>-268351</v>
       </c>
       <c r="G190" t="str">
@@ -11131,7 +11114,7 @@
         <v>43555.1</v>
       </c>
       <c r="F191" s="7">
-        <f>E191-D191</f>
+        <f t="shared" si="2"/>
         <v>-525704.1</v>
       </c>
       <c r="G191" t="str">
@@ -11160,7 +11143,7 @@
         <v>17255.3</v>
       </c>
       <c r="F192" s="7">
-        <f>E192-D192</f>
+        <f t="shared" si="2"/>
         <v>-95817.9</v>
       </c>
       <c r="G192" t="str">
@@ -11189,7 +11172,7 @@
         <v>40511.4</v>
       </c>
       <c r="F193" s="7">
-        <f>E193-D193</f>
+        <f t="shared" si="2"/>
         <v>-16550.900000000001</v>
       </c>
       <c r="G193" t="str">
@@ -11218,7 +11201,7 @@
         <v>18793.400000000001</v>
       </c>
       <c r="F194" s="7">
-        <f>E194-D194</f>
+        <f t="shared" ref="F194:F257" si="3">E194-D194</f>
         <v>-37515.599999999999</v>
       </c>
       <c r="G194" t="str">
@@ -11247,7 +11230,7 @@
         <v>36033.4</v>
       </c>
       <c r="F195" s="7">
-        <f>E195-D195</f>
+        <f t="shared" si="3"/>
         <v>-176683.9</v>
       </c>
       <c r="G195" t="str">
@@ -11276,7 +11259,7 @@
         <v>41265.4</v>
       </c>
       <c r="F196" s="7">
-        <f>E196-D196</f>
+        <f t="shared" si="3"/>
         <v>-207038.5</v>
       </c>
       <c r="G196" t="str">
@@ -11305,7 +11288,7 @@
         <v>105159.7</v>
       </c>
       <c r="F197" s="7">
-        <f>E197-D197</f>
+        <f t="shared" si="3"/>
         <v>-135661.90000000002</v>
       </c>
       <c r="G197" t="str">
@@ -11334,7 +11317,7 @@
         <v>88374</v>
       </c>
       <c r="F198" s="7">
-        <f>E198-D198</f>
+        <f t="shared" si="3"/>
         <v>-61249.299999999988</v>
       </c>
       <c r="G198" t="str">
@@ -11363,7 +11346,7 @@
         <v>60150.9</v>
       </c>
       <c r="F199" s="7">
-        <f>E199-D199</f>
+        <f t="shared" si="3"/>
         <v>-87398.5</v>
       </c>
       <c r="G199" t="str">
@@ -11392,7 +11375,7 @@
         <v>56754.6</v>
       </c>
       <c r="F200" s="7">
-        <f>E200-D200</f>
+        <f t="shared" si="3"/>
         <v>-168641.4</v>
       </c>
       <c r="G200" t="str">
@@ -11421,7 +11404,7 @@
         <v>60173.2</v>
       </c>
       <c r="F201" s="7">
-        <f>E201-D201</f>
+        <f t="shared" si="3"/>
         <v>-169039.5</v>
       </c>
       <c r="G201" t="str">
@@ -11450,7 +11433,7 @@
         <v>1837.8</v>
       </c>
       <c r="F202" s="10">
-        <f>E202-D202</f>
+        <f t="shared" si="3"/>
         <v>1832.3999999999999</v>
       </c>
       <c r="G202" t="str">
@@ -11479,7 +11462,7 @@
         <v>1011.8</v>
       </c>
       <c r="F203" s="10">
-        <f>E203-D203</f>
+        <f t="shared" si="3"/>
         <v>892.9</v>
       </c>
       <c r="G203" t="str">
@@ -11508,7 +11491,7 @@
         <v>459.9</v>
       </c>
       <c r="F204" s="10">
-        <f>E204-D204</f>
+        <f t="shared" si="3"/>
         <v>457.59999999999997</v>
       </c>
       <c r="G204" t="str">
@@ -11537,7 +11520,7 @@
         <v>682.7</v>
       </c>
       <c r="F205" s="10">
-        <f>E205-D205</f>
+        <f t="shared" si="3"/>
         <v>681.7</v>
       </c>
       <c r="G205" t="str">
@@ -11566,7 +11549,7 @@
         <v>662.8</v>
       </c>
       <c r="F206" s="10">
-        <f>E206-D206</f>
+        <f t="shared" si="3"/>
         <v>661.3</v>
       </c>
       <c r="G206" t="str">
@@ -11595,7 +11578,7 @@
         <v>709.6</v>
       </c>
       <c r="F207" s="10">
-        <f>E207-D207</f>
+        <f t="shared" si="3"/>
         <v>596.6</v>
       </c>
       <c r="G207" t="str">
@@ -11624,7 +11607,7 @@
         <v>1570487.8</v>
       </c>
       <c r="F208" s="7">
-        <f>E208-D208</f>
+        <f t="shared" si="3"/>
         <v>1566874.2</v>
       </c>
       <c r="G208" t="str">
@@ -11653,7 +11636,7 @@
         <v>1692017.8</v>
       </c>
       <c r="F209" s="7">
-        <f>E209-D209</f>
+        <f t="shared" si="3"/>
         <v>1688413.9000000001</v>
       </c>
       <c r="G209" t="str">
@@ -11682,7 +11665,7 @@
         <v>1893151.6</v>
       </c>
       <c r="F210" s="7">
-        <f>E210-D210</f>
+        <f t="shared" si="3"/>
         <v>1892349.2000000002</v>
       </c>
       <c r="G210" t="str">
@@ -11711,7 +11694,7 @@
         <v>1775385.9</v>
       </c>
       <c r="F211" s="7">
-        <f>E211-D211</f>
+        <f t="shared" si="3"/>
         <v>1755109.7999999998</v>
       </c>
       <c r="G211" t="str">
@@ -11740,7 +11723,7 @@
         <v>1783853.6</v>
       </c>
       <c r="F212" s="7">
-        <f>E212-D212</f>
+        <f t="shared" si="3"/>
         <v>1778799.8</v>
       </c>
       <c r="G212" t="str">
@@ -11769,7 +11752,7 @@
         <v>2017779.6</v>
       </c>
       <c r="F213" s="7">
-        <f>E213-D213</f>
+        <f t="shared" si="3"/>
         <v>2005477.8</v>
       </c>
       <c r="G213" t="str">
@@ -11798,7 +11781,7 @@
         <v>2047431.2</v>
       </c>
       <c r="F214" s="7">
-        <f>E214-D214</f>
+        <f t="shared" si="3"/>
         <v>2046447.9</v>
       </c>
       <c r="G214" t="str">
@@ -11827,7 +11810,7 @@
         <v>1884646.3</v>
       </c>
       <c r="F215" s="7">
-        <f>E215-D215</f>
+        <f t="shared" si="3"/>
         <v>1883492</v>
       </c>
       <c r="G215" t="str">
@@ -11856,7 +11839,7 @@
         <v>2002709.1</v>
       </c>
       <c r="F216" s="7">
-        <f>E216-D216</f>
+        <f t="shared" si="3"/>
         <v>2001218.7000000002</v>
       </c>
       <c r="G216" t="str">
@@ -11885,7 +11868,7 @@
         <v>1991015.6</v>
       </c>
       <c r="F217" s="7">
-        <f>E217-D217</f>
+        <f t="shared" si="3"/>
         <v>1989565</v>
       </c>
       <c r="G217" t="str">
@@ -11914,7 +11897,7 @@
         <v>943.3</v>
       </c>
       <c r="F218" s="7">
-        <f>E218-D218</f>
+        <f t="shared" si="3"/>
         <v>928.9</v>
       </c>
       <c r="G218" t="str">
@@ -11943,7 +11926,7 @@
         <v>2266.8000000000002</v>
       </c>
       <c r="F219" s="7">
-        <f>E219-D219</f>
+        <f t="shared" si="3"/>
         <v>2247.4</v>
       </c>
       <c r="G219" t="str">
@@ -11972,7 +11955,7 @@
         <v>2055.3000000000002</v>
       </c>
       <c r="F220" s="7">
-        <f>E220-D220</f>
+        <f t="shared" si="3"/>
         <v>2050.5</v>
       </c>
       <c r="G220" t="str">
@@ -12001,7 +11984,7 @@
         <v>1587.3</v>
       </c>
       <c r="F221" s="7">
-        <f>E221-D221</f>
+        <f t="shared" si="3"/>
         <v>1582.7</v>
       </c>
       <c r="G221" t="str">
@@ -12030,7 +12013,7 @@
         <v>2304.6</v>
       </c>
       <c r="F222" s="7">
-        <f>E222-D222</f>
+        <f t="shared" si="3"/>
         <v>2194.9</v>
       </c>
       <c r="G222" t="str">
@@ -12059,7 +12042,7 @@
         <v>3619.7</v>
       </c>
       <c r="F223" s="7">
-        <f>E223-D223</f>
+        <f t="shared" si="3"/>
         <v>3229.5</v>
       </c>
       <c r="G223" t="str">
@@ -12088,7 +12071,7 @@
         <v>2426.6999999999998</v>
       </c>
       <c r="F224" s="7">
-        <f>E224-D224</f>
+        <f t="shared" si="3"/>
         <v>1911.1</v>
       </c>
       <c r="G224" t="str">
@@ -12117,7 +12100,7 @@
         <v>2849.9</v>
       </c>
       <c r="F225" s="7">
-        <f>E225-D225</f>
+        <f t="shared" si="3"/>
         <v>2582.5</v>
       </c>
       <c r="G225" t="str">
@@ -12146,7 +12129,7 @@
         <v>2878.8</v>
       </c>
       <c r="F226" s="7">
-        <f>E226-D226</f>
+        <f t="shared" si="3"/>
         <v>2705</v>
       </c>
       <c r="G226" t="str">
@@ -12175,7 +12158,7 @@
         <v>2730.7</v>
       </c>
       <c r="F227" s="7">
-        <f>E227-D227</f>
+        <f t="shared" si="3"/>
         <v>2487.6999999999998</v>
       </c>
       <c r="G227" t="str">
@@ -12204,7 +12187,7 @@
         <v>88056.3</v>
       </c>
       <c r="F228" s="7">
-        <f>E228-D228</f>
+        <f t="shared" si="3"/>
         <v>87963.900000000009</v>
       </c>
       <c r="G228" t="str">
@@ -12233,7 +12216,7 @@
         <v>74481.7</v>
       </c>
       <c r="F229" s="7">
-        <f>E229-D229</f>
+        <f t="shared" si="3"/>
         <v>74389.5</v>
       </c>
       <c r="G229" t="str">
@@ -12262,7 +12245,7 @@
         <v>77541.100000000006</v>
       </c>
       <c r="F230" s="7">
-        <f>E230-D230</f>
+        <f t="shared" si="3"/>
         <v>77347.700000000012</v>
       </c>
       <c r="G230" t="str">
@@ -12291,7 +12274,7 @@
         <v>67516.5</v>
       </c>
       <c r="F231" s="7">
-        <f>E231-D231</f>
+        <f t="shared" si="3"/>
         <v>67474.5</v>
       </c>
       <c r="G231" t="str">
@@ -12320,7 +12303,7 @@
         <v>51887.4</v>
       </c>
       <c r="F232" s="7">
-        <f>E232-D232</f>
+        <f t="shared" si="3"/>
         <v>51612.6</v>
       </c>
       <c r="G232" t="str">
@@ -12349,7 +12332,7 @@
         <v>56933.1</v>
       </c>
       <c r="F233" s="7">
-        <f>E233-D233</f>
+        <f t="shared" si="3"/>
         <v>56605.4</v>
       </c>
       <c r="G233" t="str">
@@ -12378,7 +12361,7 @@
         <v>52201.2</v>
       </c>
       <c r="F234" s="7">
-        <f>E234-D234</f>
+        <f t="shared" si="3"/>
         <v>52091.1</v>
       </c>
       <c r="G234" t="str">
@@ -12407,7 +12390,7 @@
         <v>64009.9</v>
       </c>
       <c r="F235" s="7">
-        <f>E235-D235</f>
+        <f t="shared" si="3"/>
         <v>63862.3</v>
       </c>
       <c r="G235" t="str">
@@ -12436,7 +12419,7 @@
         <v>56516.9</v>
       </c>
       <c r="F236" s="7">
-        <f>E236-D236</f>
+        <f t="shared" si="3"/>
         <v>56397.9</v>
       </c>
       <c r="G236" t="str">
@@ -12465,7 +12448,7 @@
         <v>67454.100000000006</v>
       </c>
       <c r="F237" s="7">
-        <f>E237-D237</f>
+        <f t="shared" si="3"/>
         <v>67238.400000000009</v>
       </c>
       <c r="G237" t="str">
@@ -12494,7 +12477,7 @@
         <v>156351.29999999999</v>
       </c>
       <c r="F238" s="7">
-        <f>E238-D238</f>
+        <f t="shared" si="3"/>
         <v>52041.999999999985</v>
       </c>
       <c r="G238" t="str">
@@ -12523,7 +12506,7 @@
         <v>126659.6</v>
       </c>
       <c r="F239" s="7">
-        <f>E239-D239</f>
+        <f t="shared" si="3"/>
         <v>78137.5</v>
       </c>
       <c r="G239" t="str">
@@ -12552,7 +12535,7 @@
         <v>125779.9</v>
       </c>
       <c r="F240" s="7">
-        <f>E240-D240</f>
+        <f t="shared" si="3"/>
         <v>78323.899999999994</v>
       </c>
       <c r="G240" t="str">
@@ -12581,7 +12564,7 @@
         <v>79272.5</v>
       </c>
       <c r="F241" s="7">
-        <f>E241-D241</f>
+        <f t="shared" si="3"/>
         <v>30120.400000000001</v>
       </c>
       <c r="G241" t="str">
@@ -12610,7 +12593,7 @@
         <v>73255.3</v>
       </c>
       <c r="F242" s="7">
-        <f>E242-D242</f>
+        <f t="shared" si="3"/>
         <v>5833.6000000000058</v>
       </c>
       <c r="G242" t="str">
@@ -12639,7 +12622,7 @@
         <v>66394.2</v>
       </c>
       <c r="F243" s="7">
-        <f>E243-D243</f>
+        <f t="shared" si="3"/>
         <v>-27375.900000000009</v>
       </c>
       <c r="G243" t="str">
@@ -12668,7 +12651,7 @@
         <v>29010.7</v>
       </c>
       <c r="F244" s="7">
-        <f>E244-D244</f>
+        <f t="shared" si="3"/>
         <v>-59992.7</v>
       </c>
       <c r="G244" t="str">
@@ -12697,7 +12680,7 @@
         <v>40635.300000000003</v>
       </c>
       <c r="F245" s="7">
-        <f>E245-D245</f>
+        <f t="shared" si="3"/>
         <v>-56437.8</v>
       </c>
       <c r="G245" t="str">
@@ -12726,7 +12709,7 @@
         <v>23995.3</v>
       </c>
       <c r="F246" s="7">
-        <f>E246-D246</f>
+        <f t="shared" si="3"/>
         <v>-112053.40000000001</v>
       </c>
       <c r="G246" t="str">
@@ -12755,7 +12738,7 @@
         <v>59285.4</v>
       </c>
       <c r="F247" s="7">
-        <f>E247-D247</f>
+        <f t="shared" si="3"/>
         <v>41608</v>
       </c>
       <c r="G247" t="str">
@@ -12784,7 +12767,7 @@
         <v>276238.90000000002</v>
       </c>
       <c r="F248" s="7">
-        <f>E248-D248</f>
+        <f t="shared" si="3"/>
         <v>-204570.59999999998</v>
       </c>
       <c r="G248" t="str">
@@ -12813,7 +12796,7 @@
         <v>252794.8</v>
       </c>
       <c r="F249" s="7">
-        <f>E249-D249</f>
+        <f t="shared" si="3"/>
         <v>-201736.8</v>
       </c>
       <c r="G249" t="str">
@@ -12842,7 +12825,7 @@
         <v>237118.1</v>
       </c>
       <c r="F250" s="7">
-        <f>E250-D250</f>
+        <f t="shared" si="3"/>
         <v>-267157.69999999995</v>
       </c>
       <c r="G250" t="str">
@@ -12871,7 +12854,7 @@
         <v>334344.7</v>
       </c>
       <c r="F251" s="7">
-        <f>E251-D251</f>
+        <f t="shared" si="3"/>
         <v>-235584.60000000003</v>
       </c>
       <c r="G251" t="str">
@@ -12900,7 +12883,7 @@
         <v>399106.3</v>
       </c>
       <c r="F252" s="7">
-        <f>E252-D252</f>
+        <f t="shared" si="3"/>
         <v>89874.599999999977</v>
       </c>
       <c r="G252" t="str">
@@ -12929,7 +12912,7 @@
         <v>354271.4</v>
       </c>
       <c r="F253" s="7">
-        <f>E253-D253</f>
+        <f t="shared" si="3"/>
         <v>11543.600000000035</v>
       </c>
       <c r="G253" t="str">
@@ -12958,7 +12941,7 @@
         <v>280094.3</v>
       </c>
       <c r="F254" s="7">
-        <f>E254-D254</f>
+        <f t="shared" si="3"/>
         <v>99028.9</v>
       </c>
       <c r="G254" t="str">
@@ -12987,7 +12970,7 @@
         <v>338274</v>
       </c>
       <c r="F255" s="7">
-        <f>E255-D255</f>
+        <f t="shared" si="3"/>
         <v>108358.29999999999</v>
       </c>
       <c r="G255" t="str">
@@ -13016,7 +12999,7 @@
         <v>384521.5</v>
       </c>
       <c r="F256" s="7">
-        <f>E256-D256</f>
+        <f t="shared" si="3"/>
         <v>155278.1</v>
       </c>
       <c r="G256" t="str">
@@ -13045,7 +13028,7 @@
         <v>388764.6</v>
       </c>
       <c r="F257" s="7">
-        <f>E257-D257</f>
+        <f t="shared" si="3"/>
         <v>168814.69999999998</v>
       </c>
       <c r="G257" t="str">
@@ -13074,7 +13057,7 @@
         <v>15186.7</v>
       </c>
       <c r="F258" s="7">
-        <f>E258-D258</f>
+        <f t="shared" ref="F258:F321" si="4">E258-D258</f>
         <v>-45566.7</v>
       </c>
       <c r="G258" t="str">
@@ -13103,7 +13086,7 @@
         <v>12967.7</v>
       </c>
       <c r="F259" s="7">
-        <f>E259-D259</f>
+        <f t="shared" si="4"/>
         <v>-52616.400000000009</v>
       </c>
       <c r="G259" t="str">
@@ -13132,7 +13115,7 @@
         <v>14643.2</v>
       </c>
       <c r="F260" s="7">
-        <f>E260-D260</f>
+        <f t="shared" si="4"/>
         <v>-65288</v>
       </c>
       <c r="G260" t="str">
@@ -13161,7 +13144,7 @@
         <v>15925.4</v>
       </c>
       <c r="F261" s="7">
-        <f>E261-D261</f>
+        <f t="shared" si="4"/>
         <v>-92598</v>
       </c>
       <c r="G261" t="str">
@@ -13190,7 +13173,7 @@
         <v>15595.4</v>
       </c>
       <c r="F262" s="7">
-        <f>E262-D262</f>
+        <f t="shared" si="4"/>
         <v>-89820.800000000003</v>
       </c>
       <c r="G262" t="str">
@@ -13219,7 +13202,7 @@
         <v>10099.200000000001</v>
       </c>
       <c r="F263" s="7">
-        <f>E263-D263</f>
+        <f t="shared" si="4"/>
         <v>-111688.6</v>
       </c>
       <c r="G263" t="str">
@@ -13248,7 +13231,7 @@
         <v>10711.9</v>
       </c>
       <c r="F264" s="7">
-        <f>E264-D264</f>
+        <f t="shared" si="4"/>
         <v>-94119.3</v>
       </c>
       <c r="G264" t="str">
@@ -13277,7 +13260,7 @@
         <v>16272.3</v>
       </c>
       <c r="F265" s="7">
-        <f>E265-D265</f>
+        <f t="shared" si="4"/>
         <v>-75444.2</v>
       </c>
       <c r="G265" t="str">
@@ -13306,7 +13289,7 @@
         <v>19224.7</v>
       </c>
       <c r="F266" s="7">
-        <f>E266-D266</f>
+        <f t="shared" si="4"/>
         <v>-98443.5</v>
       </c>
       <c r="G266" t="str">
@@ -13335,7 +13318,7 @@
         <v>18569.2</v>
       </c>
       <c r="F267" s="7">
-        <f>E267-D267</f>
+        <f t="shared" si="4"/>
         <v>-98365.5</v>
       </c>
       <c r="G267" t="str">
@@ -13364,7 +13347,7 @@
         <v>29002.5</v>
       </c>
       <c r="F268" s="7">
-        <f>E268-D268</f>
+        <f t="shared" si="4"/>
         <v>-229999.6</v>
       </c>
       <c r="G268" t="str">
@@ -13393,7 +13376,7 @@
         <v>26283.9</v>
       </c>
       <c r="F269" s="7">
-        <f>E269-D269</f>
+        <f t="shared" si="4"/>
         <v>-319666.69999999995</v>
       </c>
       <c r="G269" t="str">
@@ -13422,7 +13405,7 @@
         <v>44984.6</v>
       </c>
       <c r="F270" s="7">
-        <f>E270-D270</f>
+        <f t="shared" si="4"/>
         <v>-389675.60000000003</v>
       </c>
       <c r="G270" t="str">
@@ -13451,7 +13434,7 @@
         <v>61987.5</v>
       </c>
       <c r="F271" s="7">
-        <f>E271-D271</f>
+        <f t="shared" si="4"/>
         <v>-260973.40000000002</v>
       </c>
       <c r="G271" t="str">
@@ -13480,7 +13463,7 @@
         <v>53081.3</v>
       </c>
       <c r="F272" s="7">
-        <f>E272-D272</f>
+        <f t="shared" si="4"/>
         <v>-213529.10000000003</v>
       </c>
       <c r="G272" t="str">
@@ -13509,7 +13492,7 @@
         <v>44720.800000000003</v>
       </c>
       <c r="F273" s="7">
-        <f>E273-D273</f>
+        <f t="shared" si="4"/>
         <v>-236940.7</v>
       </c>
       <c r="G273" t="str">
@@ -13538,7 +13521,7 @@
         <v>32502.7</v>
       </c>
       <c r="F274" s="7">
-        <f>E274-D274</f>
+        <f t="shared" si="4"/>
         <v>-200262</v>
       </c>
       <c r="G274" t="str">
@@ -13567,7 +13550,7 @@
         <v>71572.5</v>
       </c>
       <c r="F275" s="7">
-        <f>E275-D275</f>
+        <f t="shared" si="4"/>
         <v>6525.8000000000029</v>
       </c>
       <c r="G275" t="str">
@@ -13596,7 +13579,7 @@
         <v>112659.9</v>
       </c>
       <c r="F276" s="7">
-        <f>E276-D276</f>
+        <f t="shared" si="4"/>
         <v>16896.099999999991</v>
       </c>
       <c r="G276" t="str">
@@ -13625,7 +13608,7 @@
         <v>86760.2</v>
       </c>
       <c r="F277" s="7">
-        <f>E277-D277</f>
+        <f t="shared" si="4"/>
         <v>-5274.4000000000087</v>
       </c>
       <c r="G277" t="str">
@@ -13654,7 +13637,7 @@
         <v>107260.1</v>
       </c>
       <c r="F278" s="7">
-        <f>E278-D278</f>
+        <f t="shared" si="4"/>
         <v>-164651.19999999998</v>
       </c>
       <c r="G278" t="str">
@@ -13683,7 +13666,7 @@
         <v>108262.5</v>
       </c>
       <c r="F279" s="7">
-        <f>E279-D279</f>
+        <f t="shared" si="4"/>
         <v>-194965.3</v>
       </c>
       <c r="G279" t="str">
@@ -13712,7 +13695,7 @@
         <v>97355.4</v>
       </c>
       <c r="F280" s="7">
-        <f>E280-D280</f>
+        <f t="shared" si="4"/>
         <v>-241894.6</v>
       </c>
       <c r="G280" t="str">
@@ -13741,7 +13724,7 @@
         <v>119602.1</v>
       </c>
       <c r="F281" s="7">
-        <f>E281-D281</f>
+        <f t="shared" si="4"/>
         <v>-235353.30000000002</v>
       </c>
       <c r="G281" t="str">
@@ -13770,7 +13753,7 @@
         <v>139095.20000000001</v>
       </c>
       <c r="F282" s="7">
-        <f>E282-D282</f>
+        <f t="shared" si="4"/>
         <v>-170397.5</v>
       </c>
       <c r="G282" t="str">
@@ -13799,7 +13782,7 @@
         <v>117550.3</v>
       </c>
       <c r="F283" s="7">
-        <f>E283-D283</f>
+        <f t="shared" si="4"/>
         <v>-168676.7</v>
       </c>
       <c r="G283" t="str">
@@ -13828,7 +13811,7 @@
         <v>101050.4</v>
       </c>
       <c r="F284" s="7">
-        <f>E284-D284</f>
+        <f t="shared" si="4"/>
         <v>-164884.50000000003</v>
       </c>
       <c r="G284" t="str">
@@ -13857,7 +13840,7 @@
         <v>86563.3</v>
       </c>
       <c r="F285" s="7">
-        <f>E285-D285</f>
+        <f t="shared" si="4"/>
         <v>-157444.29999999999</v>
       </c>
       <c r="G285" t="str">
@@ -13886,7 +13869,7 @@
         <v>74506.100000000006</v>
       </c>
       <c r="F286" s="7">
-        <f>E286-D286</f>
+        <f t="shared" si="4"/>
         <v>-182461.6</v>
       </c>
       <c r="G286" t="str">
@@ -13915,7 +13898,7 @@
         <v>45038.3</v>
       </c>
       <c r="F287" s="7">
-        <f>E287-D287</f>
+        <f t="shared" si="4"/>
         <v>-207579.2</v>
       </c>
       <c r="G287" t="str">
@@ -13944,7 +13927,7 @@
         <v>162085.1</v>
       </c>
       <c r="F288" s="7">
-        <f>E288-D288</f>
+        <f t="shared" si="4"/>
         <v>158424.80000000002</v>
       </c>
       <c r="G288" t="str">
@@ -13973,7 +13956,7 @@
         <v>153831.1</v>
       </c>
       <c r="F289" s="7">
-        <f>E289-D289</f>
+        <f t="shared" si="4"/>
         <v>150391.80000000002</v>
       </c>
       <c r="G289" t="str">
@@ -14002,7 +13985,7 @@
         <v>146525.5</v>
       </c>
       <c r="F290" s="7">
-        <f>E290-D290</f>
+        <f t="shared" si="4"/>
         <v>108376.7</v>
       </c>
       <c r="G290" t="str">
@@ -14031,7 +14014,7 @@
         <v>138966.6</v>
       </c>
       <c r="F291" s="7">
-        <f>E291-D291</f>
+        <f t="shared" si="4"/>
         <v>89740.800000000003</v>
       </c>
       <c r="G291" t="str">
@@ -14060,7 +14043,7 @@
         <v>179092.1</v>
       </c>
       <c r="F292" s="7">
-        <f>E292-D292</f>
+        <f t="shared" si="4"/>
         <v>142775.40000000002</v>
       </c>
       <c r="G292" t="str">
@@ -14089,7 +14072,7 @@
         <v>111996.5</v>
       </c>
       <c r="F293" s="7">
-        <f>E293-D293</f>
+        <f t="shared" si="4"/>
         <v>24307.399999999994</v>
       </c>
       <c r="G293" t="str">
@@ -14118,7 +14101,7 @@
         <v>20493.2</v>
       </c>
       <c r="F294" s="7">
-        <f>E294-D294</f>
+        <f t="shared" si="4"/>
         <v>-104322.8</v>
       </c>
       <c r="G294" t="str">
@@ -14147,7 +14130,7 @@
         <v>124649.3</v>
       </c>
       <c r="F295" s="7">
-        <f>E295-D295</f>
+        <f t="shared" si="4"/>
         <v>99769</v>
       </c>
       <c r="G295" t="str">
@@ -14176,7 +14159,7 @@
         <v>72154.100000000006</v>
       </c>
       <c r="F296" s="7">
-        <f>E296-D296</f>
+        <f t="shared" si="4"/>
         <v>-24672.199999999997</v>
       </c>
       <c r="G296" t="str">
@@ -14205,7 +14188,7 @@
         <v>57758.400000000001</v>
       </c>
       <c r="F297" s="7">
-        <f>E297-D297</f>
+        <f t="shared" si="4"/>
         <v>22181.5</v>
       </c>
       <c r="G297" t="str">
@@ -14234,7 +14217,7 @@
         <v>55.8</v>
       </c>
       <c r="F298" s="7">
-        <f>E298-D298</f>
+        <f t="shared" si="4"/>
         <v>-62</v>
       </c>
       <c r="G298" t="str">
@@ -14263,7 +14246,7 @@
         <v>63.1</v>
       </c>
       <c r="F299" s="7">
-        <f>E299-D299</f>
+        <f t="shared" si="4"/>
         <v>-8.1999999999999957</v>
       </c>
       <c r="G299" t="str">
@@ -14292,7 +14275,7 @@
         <v>60</v>
       </c>
       <c r="F300" s="7">
-        <f>E300-D300</f>
+        <f t="shared" si="4"/>
         <v>-67.3</v>
       </c>
       <c r="G300" t="str">
@@ -14321,7 +14304,7 @@
         <v>59</v>
       </c>
       <c r="F301" s="7">
-        <f>E301-D301</f>
+        <f t="shared" si="4"/>
         <v>-129.4</v>
       </c>
       <c r="G301" t="str">
@@ -14350,7 +14333,7 @@
         <v>46.3</v>
       </c>
       <c r="F302" s="7">
-        <f>E302-D302</f>
+        <f t="shared" si="4"/>
         <v>-115.2</v>
       </c>
       <c r="G302" t="str">
@@ -14379,7 +14362,7 @@
         <v>58</v>
       </c>
       <c r="F303" s="7">
-        <f>E303-D303</f>
+        <f t="shared" si="4"/>
         <v>-286.89999999999998</v>
       </c>
       <c r="G303" t="str">
@@ -14408,7 +14391,7 @@
         <v>58.9</v>
       </c>
       <c r="F304" s="7">
-        <f>E304-D304</f>
+        <f t="shared" si="4"/>
         <v>-142.79999999999998</v>
       </c>
       <c r="G304" t="str">
@@ -14437,7 +14420,7 @@
         <v>42.4</v>
       </c>
       <c r="F305" s="7">
-        <f>E305-D305</f>
+        <f t="shared" si="4"/>
         <v>-141.1</v>
       </c>
       <c r="G305" t="str">
@@ -14466,7 +14449,7 @@
         <v>51.9</v>
       </c>
       <c r="F306" s="7">
-        <f>E306-D306</f>
+        <f t="shared" si="4"/>
         <v>11.5</v>
       </c>
       <c r="G306" t="str">
@@ -14495,7 +14478,7 @@
         <v>50.8</v>
       </c>
       <c r="F307" s="7">
-        <f>E307-D307</f>
+        <f t="shared" si="4"/>
         <v>14.5</v>
       </c>
       <c r="G307" t="str">
@@ -14524,7 +14507,7 @@
         <v>134626.29999999999</v>
       </c>
       <c r="F308" s="7">
-        <f>E308-D308</f>
+        <f t="shared" si="4"/>
         <v>129653.59999999999</v>
       </c>
       <c r="G308" t="str">
@@ -14553,7 +14536,7 @@
         <v>118890.1</v>
       </c>
       <c r="F309" s="7">
-        <f>E309-D309</f>
+        <f t="shared" si="4"/>
         <v>113740.6</v>
       </c>
       <c r="G309" t="str">
@@ -14582,7 +14565,7 @@
         <v>102724.2</v>
       </c>
       <c r="F310" s="7">
-        <f>E310-D310</f>
+        <f t="shared" si="4"/>
         <v>83904.1</v>
       </c>
       <c r="G310" t="str">
@@ -14611,7 +14594,7 @@
         <v>71777.8</v>
       </c>
       <c r="F311" s="7">
-        <f>E311-D311</f>
+        <f t="shared" si="4"/>
         <v>-71888.400000000009</v>
       </c>
       <c r="G311" t="str">
@@ -14640,7 +14623,7 @@
         <v>68528.3</v>
       </c>
       <c r="F312" s="7">
-        <f>E312-D312</f>
+        <f t="shared" si="4"/>
         <v>-55909.3</v>
       </c>
       <c r="G312" t="str">
@@ -14669,7 +14652,7 @@
         <v>61679.1</v>
       </c>
       <c r="F313" s="7">
-        <f>E313-D313</f>
+        <f t="shared" si="4"/>
         <v>-55770.500000000007</v>
       </c>
       <c r="G313" t="str">
@@ -14698,7 +14681,7 @@
         <v>49649.2</v>
       </c>
       <c r="F314" s="7">
-        <f>E314-D314</f>
+        <f t="shared" si="4"/>
         <v>-17133.100000000006</v>
       </c>
       <c r="G314" t="str">
@@ -14727,7 +14710,7 @@
         <v>57417.8</v>
       </c>
       <c r="F315" s="7">
-        <f>E315-D315</f>
+        <f t="shared" si="4"/>
         <v>19090.5</v>
       </c>
       <c r="G315" t="str">
@@ -14756,7 +14739,7 @@
         <v>56510.9</v>
       </c>
       <c r="F316" s="7">
-        <f>E316-D316</f>
+        <f t="shared" si="4"/>
         <v>13832.800000000003</v>
       </c>
       <c r="G316" t="str">
@@ -14785,7 +14768,7 @@
         <v>51458.5</v>
       </c>
       <c r="F317" s="7">
-        <f>E317-D317</f>
+        <f t="shared" si="4"/>
         <v>39500.6</v>
       </c>
       <c r="G317" t="str">
@@ -14814,7 +14797,7 @@
         <v>71227</v>
       </c>
       <c r="F318" s="10">
-        <f>E318-D318</f>
+        <f t="shared" si="4"/>
         <v>21526.400000000001</v>
       </c>
       <c r="G318" t="str">
@@ -14843,7 +14826,7 @@
         <v>67959.100000000006</v>
       </c>
       <c r="F319" s="10">
-        <f>E319-D319</f>
+        <f t="shared" si="4"/>
         <v>21410.500000000007</v>
       </c>
       <c r="G319" t="str">
@@ -14872,7 +14855,7 @@
         <v>75440.5</v>
       </c>
       <c r="F320" s="10">
-        <f>E320-D320</f>
+        <f t="shared" si="4"/>
         <v>33244.9</v>
       </c>
       <c r="G320" t="str">
@@ -14901,7 +14884,7 @@
         <v>81273.7</v>
       </c>
       <c r="F321" s="10">
-        <f>E321-D321</f>
+        <f t="shared" si="4"/>
         <v>43964.6</v>
       </c>
       <c r="G321" t="str">
@@ -14930,7 +14913,7 @@
         <v>95229.3</v>
       </c>
       <c r="F322" s="10">
-        <f>E322-D322</f>
+        <f t="shared" ref="F322:F385" si="5">E322-D322</f>
         <v>62442.5</v>
       </c>
       <c r="G322" t="str">
@@ -14959,7 +14942,7 @@
         <v>102628.4</v>
       </c>
       <c r="F323" s="10">
-        <f>E323-D323</f>
+        <f t="shared" si="5"/>
         <v>75688.899999999994</v>
       </c>
       <c r="G323" t="str">
@@ -14988,7 +14971,7 @@
         <v>81871.600000000006</v>
       </c>
       <c r="F324" s="10">
-        <f>E324-D324</f>
+        <f t="shared" si="5"/>
         <v>51537.8</v>
       </c>
       <c r="G324" t="str">
@@ -15017,7 +15000,7 @@
         <v>82633</v>
       </c>
       <c r="F325" s="10">
-        <f>E325-D325</f>
+        <f t="shared" si="5"/>
         <v>42653.8</v>
       </c>
       <c r="G325" t="str">
@@ -15046,7 +15029,7 @@
         <v>102562.8</v>
       </c>
       <c r="F326" s="10">
-        <f>E326-D326</f>
+        <f t="shared" si="5"/>
         <v>47584</v>
       </c>
       <c r="G326" t="str">
@@ -15075,7 +15058,7 @@
         <v>102689.9</v>
       </c>
       <c r="F327" s="10">
-        <f>E327-D327</f>
+        <f t="shared" si="5"/>
         <v>55890.7</v>
       </c>
       <c r="G327" t="str">
@@ -15104,7 +15087,7 @@
         <v>11.2</v>
       </c>
       <c r="F328" s="7">
-        <f>E328-D328</f>
+        <f t="shared" si="5"/>
         <v>-161.20000000000002</v>
       </c>
       <c r="G328" t="str">
@@ -15133,7 +15116,7 @@
         <v>490.1</v>
       </c>
       <c r="F329" s="7">
-        <f>E329-D329</f>
+        <f t="shared" si="5"/>
         <v>351.1</v>
       </c>
       <c r="G329" t="str">
@@ -15162,7 +15145,7 @@
         <v>578.79999999999995</v>
       </c>
       <c r="F330" s="7">
-        <f>E330-D330</f>
+        <f t="shared" si="5"/>
         <v>455.09999999999997</v>
       </c>
       <c r="G330" t="str">
@@ -15191,7 +15174,7 @@
         <v>594.79999999999995</v>
       </c>
       <c r="F331" s="7">
-        <f>E331-D331</f>
+        <f t="shared" si="5"/>
         <v>438.49999999999994</v>
       </c>
       <c r="G331" t="str">
@@ -15220,7 +15203,7 @@
         <v>490</v>
       </c>
       <c r="F332" s="7">
-        <f>E332-D332</f>
+        <f t="shared" si="5"/>
         <v>438.4</v>
       </c>
       <c r="G332" t="str">
@@ -15249,7 +15232,7 @@
         <v>359.8</v>
       </c>
       <c r="F333" s="7">
-        <f>E333-D333</f>
+        <f t="shared" si="5"/>
         <v>315.5</v>
       </c>
       <c r="G333" t="str">
@@ -15278,7 +15261,7 @@
         <v>337.5</v>
       </c>
       <c r="F334" s="7">
-        <f>E334-D334</f>
+        <f t="shared" si="5"/>
         <v>305.3</v>
       </c>
       <c r="G334" t="str">
@@ -15307,7 +15290,7 @@
         <v>384.1</v>
       </c>
       <c r="F335" s="7">
-        <f>E335-D335</f>
+        <f t="shared" si="5"/>
         <v>309.8</v>
       </c>
       <c r="G335" t="str">
@@ -15336,7 +15319,7 @@
         <v>346.8</v>
       </c>
       <c r="F336" s="7">
-        <f>E336-D336</f>
+        <f t="shared" si="5"/>
         <v>261.20000000000005</v>
       </c>
       <c r="G336" t="str">
@@ -15365,7 +15348,7 @@
         <v>374</v>
       </c>
       <c r="F337" s="7">
-        <f>E337-D337</f>
+        <f t="shared" si="5"/>
         <v>258.89999999999998</v>
       </c>
       <c r="G337" t="str">
@@ -15394,7 +15377,7 @@
         <v>77.3</v>
       </c>
       <c r="F338" s="7">
-        <f>E338-D338</f>
+        <f t="shared" si="5"/>
         <v>77.3</v>
       </c>
       <c r="G338" t="str">
@@ -15423,7 +15406,7 @@
         <v>19.8</v>
       </c>
       <c r="F339" s="7">
-        <f>E339-D339</f>
+        <f t="shared" si="5"/>
         <v>19.8</v>
       </c>
       <c r="G339" t="str">
@@ -15452,7 +15435,7 @@
         <v>13.6</v>
       </c>
       <c r="F340" s="7">
-        <f>E340-D340</f>
+        <f t="shared" si="5"/>
         <v>13.6</v>
       </c>
       <c r="G340" t="str">
@@ -15481,7 +15464,7 @@
         <v>33.4</v>
       </c>
       <c r="F341" s="7">
-        <f>E341-D341</f>
+        <f t="shared" si="5"/>
         <v>33.4</v>
       </c>
       <c r="G341" t="str">
@@ -15510,7 +15493,7 @@
         <v>25.6</v>
       </c>
       <c r="F342" s="7">
-        <f>E342-D342</f>
+        <f t="shared" si="5"/>
         <v>25.400000000000002</v>
       </c>
       <c r="G342" t="str">
@@ -15539,7 +15522,7 @@
         <v>19.3</v>
       </c>
       <c r="F343" s="7">
-        <f>E343-D343</f>
+        <f t="shared" si="5"/>
         <v>19.3</v>
       </c>
       <c r="G343" t="str">
@@ -15568,7 +15551,7 @@
         <v>29</v>
       </c>
       <c r="F344" s="7">
-        <f>E344-D344</f>
+        <f t="shared" si="5"/>
         <v>28.8</v>
       </c>
       <c r="G344" t="str">
@@ -15597,7 +15580,7 @@
         <v>31.2</v>
       </c>
       <c r="F345" s="7">
-        <f>E345-D345</f>
+        <f t="shared" si="5"/>
         <v>31.2</v>
       </c>
       <c r="G345" t="str">
@@ -15626,7 +15609,7 @@
         <v>37.9</v>
       </c>
       <c r="F346" s="7">
-        <f>E346-D346</f>
+        <f t="shared" si="5"/>
         <v>37.5</v>
       </c>
       <c r="G346" t="str">
@@ -15655,7 +15638,7 @@
         <v>39.1</v>
       </c>
       <c r="F347" s="7">
-        <f>E347-D347</f>
+        <f t="shared" si="5"/>
         <v>39.1</v>
       </c>
       <c r="G347" t="str">
@@ -15684,7 +15667,7 @@
         <v>1193.0999999999999</v>
       </c>
       <c r="F348" s="7">
-        <f>E348-D348</f>
+        <f t="shared" si="5"/>
         <v>1193.0999999999999</v>
       </c>
       <c r="G348" t="str">
@@ -15713,7 +15696,7 @@
         <v>1378.5</v>
       </c>
       <c r="F349" s="7">
-        <f>E349-D349</f>
+        <f t="shared" si="5"/>
         <v>783.5</v>
       </c>
       <c r="G349" t="str">
@@ -15742,7 +15725,7 @@
         <v>485.6</v>
       </c>
       <c r="F350" s="7">
-        <f>E350-D350</f>
+        <f t="shared" si="5"/>
         <v>485.6</v>
       </c>
       <c r="G350" t="str">
@@ -15771,7 +15754,7 @@
         <v>564.9</v>
       </c>
       <c r="F351" s="7">
-        <f>E351-D351</f>
+        <f t="shared" si="5"/>
         <v>564.9</v>
       </c>
       <c r="G351" t="str">
@@ -15800,7 +15783,7 @@
         <v>1815.6</v>
       </c>
       <c r="F352" s="7">
-        <f>E352-D352</f>
+        <f t="shared" si="5"/>
         <v>-319.40000000000009</v>
       </c>
       <c r="G352" t="str">
@@ -15829,7 +15812,7 @@
         <v>991.9</v>
       </c>
       <c r="F353" s="7">
-        <f>E353-D353</f>
+        <f t="shared" si="5"/>
         <v>-513.1</v>
       </c>
       <c r="G353" t="str">
@@ -15858,7 +15841,7 @@
         <v>1183.4000000000001</v>
       </c>
       <c r="F354" s="7">
-        <f>E354-D354</f>
+        <f t="shared" si="5"/>
         <v>1183.4000000000001</v>
       </c>
       <c r="G354" t="str">
@@ -15887,7 +15870,7 @@
         <v>126.8</v>
       </c>
       <c r="F355" s="7">
-        <f>E355-D355</f>
+        <f t="shared" si="5"/>
         <v>-5123.2</v>
       </c>
       <c r="G355" t="str">
@@ -15916,7 +15899,7 @@
         <v>459.2</v>
       </c>
       <c r="F356" s="7">
-        <f>E356-D356</f>
+        <f t="shared" si="5"/>
         <v>-4440.8</v>
       </c>
       <c r="G356" t="str">
@@ -15945,7 +15928,7 @@
         <v>106.6</v>
       </c>
       <c r="F357" s="7">
-        <f>E357-D357</f>
+        <f t="shared" si="5"/>
         <v>106.6</v>
       </c>
       <c r="G357" t="str">
@@ -15974,7 +15957,7 @@
         <v>8932.7999999999993</v>
       </c>
       <c r="F358" s="7">
-        <f>E358-D358</f>
+        <f t="shared" si="5"/>
         <v>-227219.90000000002</v>
       </c>
       <c r="G358" t="str">
@@ -16003,7 +15986,7 @@
         <v>15945.3</v>
       </c>
       <c r="F359" s="7">
-        <f>E359-D359</f>
+        <f t="shared" si="5"/>
         <v>-271461.5</v>
       </c>
       <c r="G359" t="str">
@@ -16032,7 +16015,7 @@
         <v>17884.900000000001</v>
       </c>
       <c r="F360" s="7">
-        <f>E360-D360</f>
+        <f t="shared" si="5"/>
         <v>-310496.5</v>
       </c>
       <c r="G360" t="str">
@@ -16061,7 +16044,7 @@
         <v>20760.5</v>
       </c>
       <c r="F361" s="7">
-        <f>E361-D361</f>
+        <f t="shared" si="5"/>
         <v>-198966.1</v>
       </c>
       <c r="G361" t="str">
@@ -16090,7 +16073,7 @@
         <v>7938</v>
       </c>
       <c r="F362" s="7">
-        <f>E362-D362</f>
+        <f t="shared" si="5"/>
         <v>-205751.1</v>
       </c>
       <c r="G362" t="str">
@@ -16119,7 +16102,7 @@
         <v>6970.7</v>
       </c>
       <c r="F363" s="7">
-        <f>E363-D363</f>
+        <f t="shared" si="5"/>
         <v>-222168.69999999998</v>
       </c>
       <c r="G363" t="str">
@@ -16148,7 +16131,7 @@
         <v>52.1</v>
       </c>
       <c r="F364" s="7">
-        <f>E364-D364</f>
+        <f t="shared" si="5"/>
         <v>-210990.1</v>
       </c>
       <c r="G364" t="str">
@@ -16177,7 +16160,7 @@
         <v>8.1</v>
       </c>
       <c r="F365" s="7">
-        <f>E365-D365</f>
+        <f t="shared" si="5"/>
         <v>-108851.9</v>
       </c>
       <c r="G365" t="str">
@@ -16206,7 +16189,7 @@
         <v>2017.6</v>
       </c>
       <c r="F366" s="7">
-        <f>E366-D366</f>
+        <f t="shared" si="5"/>
         <v>-131341.19999999998</v>
       </c>
       <c r="G366" t="str">
@@ -16235,7 +16218,7 @@
         <v>1954.1</v>
       </c>
       <c r="F367" s="7">
-        <f>E367-D367</f>
+        <f t="shared" si="5"/>
         <v>-157781.5</v>
       </c>
       <c r="G367" t="str">
@@ -16264,7 +16247,7 @@
         <v>15515.7</v>
       </c>
       <c r="F368" s="7">
-        <f>E368-D368</f>
+        <f t="shared" si="5"/>
         <v>14394</v>
       </c>
       <c r="G368" t="str">
@@ -16293,7 +16276,7 @@
         <v>30233.1</v>
       </c>
       <c r="F369" s="7">
-        <f>E369-D369</f>
+        <f t="shared" si="5"/>
         <v>29043</v>
       </c>
       <c r="G369" t="str">
@@ -16322,7 +16305,7 @@
         <v>6672.6</v>
       </c>
       <c r="F370" s="7">
-        <f>E370-D370</f>
+        <f t="shared" si="5"/>
         <v>5418.5</v>
       </c>
       <c r="G370" t="str">
@@ -16351,7 +16334,7 @@
         <v>5039.3</v>
       </c>
       <c r="F371" s="7">
-        <f>E371-D371</f>
+        <f t="shared" si="5"/>
         <v>2636.4</v>
       </c>
       <c r="G371" t="str">
@@ -16380,7 +16363,7 @@
         <v>7723.8</v>
       </c>
       <c r="F372" s="7">
-        <f>E372-D372</f>
+        <f t="shared" si="5"/>
         <v>6815.6</v>
       </c>
       <c r="G372" t="str">
@@ -16409,7 +16392,7 @@
         <v>13859</v>
       </c>
       <c r="F373" s="7">
-        <f>E373-D373</f>
+        <f t="shared" si="5"/>
         <v>13558.1</v>
       </c>
       <c r="G373" t="str">
@@ -16438,7 +16421,7 @@
         <v>7691.6</v>
       </c>
       <c r="F374" s="7">
-        <f>E374-D374</f>
+        <f t="shared" si="5"/>
         <v>4261.1000000000004</v>
       </c>
       <c r="G374" t="str">
@@ -16467,7 +16450,7 @@
         <v>6186.3</v>
       </c>
       <c r="F375" s="7">
-        <f>E375-D375</f>
+        <f t="shared" si="5"/>
         <v>6021.9000000000005</v>
       </c>
       <c r="G375" t="str">
@@ -16496,7 +16479,7 @@
         <v>8026.6</v>
       </c>
       <c r="F376" s="7">
-        <f>E376-D376</f>
+        <f t="shared" si="5"/>
         <v>7875.9000000000005</v>
       </c>
       <c r="G376" t="str">
@@ -16525,7 +16508,7 @@
         <v>9967.9</v>
       </c>
       <c r="F377" s="7">
-        <f>E377-D377</f>
+        <f t="shared" si="5"/>
         <v>9798</v>
       </c>
       <c r="G377" t="str">
@@ -16554,7 +16537,7 @@
         <v>58774.5</v>
       </c>
       <c r="F378" s="7">
-        <f>E378-D378</f>
+        <f t="shared" si="5"/>
         <v>-120092.20000000001</v>
       </c>
       <c r="G378" t="str">
@@ -16583,7 +16566,7 @@
         <v>63904.800000000003</v>
       </c>
       <c r="F379" s="7">
-        <f>E379-D379</f>
+        <f t="shared" si="5"/>
         <v>-98954.900000000009</v>
       </c>
       <c r="G379" t="str">
@@ -16612,7 +16595,7 @@
         <v>47188.4</v>
       </c>
       <c r="F380" s="7">
-        <f>E380-D380</f>
+        <f t="shared" si="5"/>
         <v>-100575.4</v>
       </c>
       <c r="G380" t="str">
@@ -16641,7 +16624,7 @@
         <v>69406.600000000006</v>
       </c>
       <c r="F381" s="7">
-        <f>E381-D381</f>
+        <f t="shared" si="5"/>
         <v>-112807.69999999998</v>
       </c>
       <c r="G381" t="str">
@@ -16670,7 +16653,7 @@
         <v>53104.1</v>
       </c>
       <c r="F382" s="7">
-        <f>E382-D382</f>
+        <f t="shared" si="5"/>
         <v>-147043</v>
       </c>
       <c r="G382" t="str">
@@ -16699,7 +16682,7 @@
         <v>107717.2</v>
       </c>
       <c r="F383" s="7">
-        <f>E383-D383</f>
+        <f t="shared" si="5"/>
         <v>-3120.1999999999971</v>
       </c>
       <c r="G383" t="str">
@@ -16728,7 +16711,7 @@
         <v>109782</v>
       </c>
       <c r="F384" s="7">
-        <f>E384-D384</f>
+        <f t="shared" si="5"/>
         <v>-9097.5</v>
       </c>
       <c r="G384" t="str">
@@ -16757,7 +16740,7 @@
         <v>56707.4</v>
       </c>
       <c r="F385" s="7">
-        <f>E385-D385</f>
+        <f t="shared" si="5"/>
         <v>-62949.700000000004</v>
       </c>
       <c r="G385" t="str">
@@ -16786,7 +16769,7 @@
         <v>101764</v>
       </c>
       <c r="F386" s="7">
-        <f>E386-D386</f>
+        <f t="shared" ref="F386:F449" si="6">E386-D386</f>
         <v>-47267.399999999994</v>
       </c>
       <c r="G386" t="str">
@@ -16815,7 +16798,7 @@
         <v>57484.7</v>
       </c>
       <c r="F387" s="7">
-        <f>E387-D387</f>
+        <f t="shared" si="6"/>
         <v>-82157.000000000015</v>
       </c>
       <c r="G387" t="str">
@@ -16844,7 +16827,7 @@
         <v>77850</v>
       </c>
       <c r="F388" s="10">
-        <f>E388-D388</f>
+        <f t="shared" si="6"/>
         <v>77557.5</v>
       </c>
       <c r="G388" t="str">
@@ -16873,7 +16856,7 @@
         <v>63266.9</v>
       </c>
       <c r="F389" s="10">
-        <f>E389-D389</f>
+        <f t="shared" si="6"/>
         <v>62966.6</v>
       </c>
       <c r="G389" t="str">
@@ -16902,7 +16885,7 @@
         <v>54292.4</v>
       </c>
       <c r="F390" s="10">
-        <f>E390-D390</f>
+        <f t="shared" si="6"/>
         <v>53893.200000000004</v>
       </c>
       <c r="G390" t="str">
@@ -16931,7 +16914,7 @@
         <v>34345.300000000003</v>
       </c>
       <c r="F391" s="10">
-        <f>E391-D391</f>
+        <f t="shared" si="6"/>
         <v>33876.300000000003</v>
       </c>
       <c r="G391" t="str">
@@ -16960,7 +16943,7 @@
         <v>33149.199999999997</v>
       </c>
       <c r="F392" s="10">
-        <f>E392-D392</f>
+        <f t="shared" si="6"/>
         <v>24689.199999999997</v>
       </c>
       <c r="G392" t="str">
@@ -16989,7 +16972,7 @@
         <v>30896.6</v>
       </c>
       <c r="F393" s="10">
-        <f>E393-D393</f>
+        <f t="shared" si="6"/>
         <v>28142.5</v>
       </c>
       <c r="G393" t="str">
@@ -17018,7 +17001,7 @@
         <v>24998.1</v>
       </c>
       <c r="F394" s="10">
-        <f>E394-D394</f>
+        <f t="shared" si="6"/>
         <v>16404.099999999999</v>
       </c>
       <c r="G394" t="str">
@@ -17047,7 +17030,7 @@
         <v>32542.5</v>
       </c>
       <c r="F395" s="10">
-        <f>E395-D395</f>
+        <f t="shared" si="6"/>
         <v>25519.8</v>
       </c>
       <c r="G395" t="str">
@@ -17076,7 +17059,7 @@
         <v>39088.400000000001</v>
       </c>
       <c r="F396" s="10">
-        <f>E396-D396</f>
+        <f t="shared" si="6"/>
         <v>31568.2</v>
       </c>
       <c r="G396" t="str">
@@ -17105,7 +17088,7 @@
         <v>55959.4</v>
       </c>
       <c r="F397" s="10">
-        <f>E397-D397</f>
+        <f t="shared" si="6"/>
         <v>53054.9</v>
       </c>
       <c r="G397" t="str">
@@ -17134,7 +17117,7 @@
         <v>50863.6</v>
       </c>
       <c r="F398" s="7">
-        <f>E398-D398</f>
+        <f t="shared" si="6"/>
         <v>50751.299999999996</v>
       </c>
       <c r="G398" t="str">
@@ -17163,7 +17146,7 @@
         <v>84351.8</v>
       </c>
       <c r="F399" s="7">
-        <f>E399-D399</f>
+        <f t="shared" si="6"/>
         <v>77240.100000000006</v>
       </c>
       <c r="G399" t="str">
@@ -17192,7 +17175,7 @@
         <v>67695.3</v>
       </c>
       <c r="F400" s="7">
-        <f>E400-D400</f>
+        <f t="shared" si="6"/>
         <v>62680.5</v>
       </c>
       <c r="G400" t="str">
@@ -17221,7 +17204,7 @@
         <v>70882.2</v>
       </c>
       <c r="F401" s="7">
-        <f>E401-D401</f>
+        <f t="shared" si="6"/>
         <v>60603.399999999994</v>
       </c>
       <c r="G401" t="str">
@@ -17250,7 +17233,7 @@
         <v>82241.5</v>
       </c>
       <c r="F402" s="7">
-        <f>E402-D402</f>
+        <f t="shared" si="6"/>
         <v>7412.3999999999942</v>
       </c>
       <c r="G402" t="str">
@@ -17279,7 +17262,7 @@
         <v>52447.6</v>
       </c>
       <c r="F403" s="7">
-        <f>E403-D403</f>
+        <f t="shared" si="6"/>
         <v>-117177.4</v>
       </c>
       <c r="G403" t="str">
@@ -17308,7 +17291,7 @@
         <v>48832.800000000003</v>
       </c>
       <c r="F404" s="7">
-        <f>E404-D404</f>
+        <f t="shared" si="6"/>
         <v>-41175.5</v>
       </c>
       <c r="G404" t="str">
@@ -17337,7 +17320,7 @@
         <v>72797.600000000006</v>
       </c>
       <c r="F405" s="7">
-        <f>E405-D405</f>
+        <f t="shared" si="6"/>
         <v>-93562.6</v>
       </c>
       <c r="G405" t="str">
@@ -17366,7 +17349,7 @@
         <v>34632.199999999997</v>
       </c>
       <c r="F406" s="7">
-        <f>E406-D406</f>
+        <f t="shared" si="6"/>
         <v>-75801.900000000009</v>
       </c>
       <c r="G406" t="str">
@@ -17395,7 +17378,7 @@
         <v>27284.7</v>
       </c>
       <c r="F407" s="7">
-        <f>E407-D407</f>
+        <f t="shared" si="6"/>
         <v>-116974.2</v>
       </c>
       <c r="G407" t="str">
@@ -17424,7 +17407,7 @@
         <v>23492.799999999999</v>
       </c>
       <c r="F408" s="7">
-        <f>E408-D408</f>
+        <f t="shared" si="6"/>
         <v>-10511.399999999998</v>
       </c>
       <c r="G408" t="str">
@@ -17453,7 +17436,7 @@
         <v>23581.200000000001</v>
       </c>
       <c r="F409" s="7">
-        <f>E409-D409</f>
+        <f t="shared" si="6"/>
         <v>9575.4000000000015</v>
       </c>
       <c r="G409" t="str">
@@ -17482,7 +17465,7 @@
         <v>37564</v>
       </c>
       <c r="F410" s="7">
-        <f>E410-D410</f>
+        <f t="shared" si="6"/>
         <v>19802.900000000001</v>
       </c>
       <c r="G410" t="str">
@@ -17511,7 +17494,7 @@
         <v>47365.9</v>
       </c>
       <c r="F411" s="7">
-        <f>E411-D411</f>
+        <f t="shared" si="6"/>
         <v>24528.5</v>
       </c>
       <c r="G411" t="str">
@@ -17540,7 +17523,7 @@
         <v>34719.300000000003</v>
       </c>
       <c r="F412" s="7">
-        <f>E412-D412</f>
+        <f t="shared" si="6"/>
         <v>-4296.5999999999985</v>
       </c>
       <c r="G412" t="str">
@@ -17569,7 +17552,7 @@
         <v>28537</v>
       </c>
       <c r="F413" s="7">
-        <f>E413-D413</f>
+        <f t="shared" si="6"/>
         <v>5831.4000000000015</v>
       </c>
       <c r="G413" t="str">
@@ -17598,7 +17581,7 @@
         <v>24129.200000000001</v>
       </c>
       <c r="F414" s="7">
-        <f>E414-D414</f>
+        <f t="shared" si="6"/>
         <v>-4500.2999999999993</v>
       </c>
       <c r="G414" t="str">
@@ -17627,7 +17610,7 @@
         <v>35788.400000000001</v>
       </c>
       <c r="F415" s="7">
-        <f>E415-D415</f>
+        <f t="shared" si="6"/>
         <v>100.59999999999854</v>
       </c>
       <c r="G415" t="str">
@@ -17656,7 +17639,7 @@
         <v>38428</v>
       </c>
       <c r="F416" s="7">
-        <f>E416-D416</f>
+        <f t="shared" si="6"/>
         <v>15562.900000000001</v>
       </c>
       <c r="G416" t="str">
@@ -17685,7 +17668,7 @@
         <v>32383.9</v>
       </c>
       <c r="F417" s="7">
-        <f>E417-D417</f>
+        <f t="shared" si="6"/>
         <v>-15756.5</v>
       </c>
       <c r="G417" t="str">
@@ -17714,7 +17697,7 @@
         <v>9909.2000000000007</v>
       </c>
       <c r="F418" s="7">
-        <f>E418-D418</f>
+        <f t="shared" si="6"/>
         <v>-11216.599999999999</v>
       </c>
       <c r="G418" t="str">
@@ -17743,7 +17726,7 @@
         <v>8047.7</v>
       </c>
       <c r="F419" s="7">
-        <f>E419-D419</f>
+        <f t="shared" si="6"/>
         <v>-8231.9000000000015</v>
       </c>
       <c r="G419" t="str">
@@ -17772,7 +17755,7 @@
         <v>10772.7</v>
       </c>
       <c r="F420" s="7">
-        <f>E420-D420</f>
+        <f t="shared" si="6"/>
         <v>-9939.2000000000007</v>
       </c>
       <c r="G420" t="str">
@@ -17801,7 +17784,7 @@
         <v>11288.8</v>
       </c>
       <c r="F421" s="7">
-        <f>E421-D421</f>
+        <f t="shared" si="6"/>
         <v>-5191.6000000000022</v>
       </c>
       <c r="G421" t="str">
@@ -17830,7 +17813,7 @@
         <v>13472.8</v>
       </c>
       <c r="F422" s="7">
-        <f>E422-D422</f>
+        <f t="shared" si="6"/>
         <v>-2036</v>
       </c>
       <c r="G422" t="str">
@@ -17859,7 +17842,7 @@
         <v>8195.1</v>
       </c>
       <c r="F423" s="7">
-        <f>E423-D423</f>
+        <f t="shared" si="6"/>
         <v>-1147.6000000000004</v>
       </c>
       <c r="G423" t="str">
@@ -17888,7 +17871,7 @@
         <v>7030.3</v>
       </c>
       <c r="F424" s="7">
-        <f>E424-D424</f>
+        <f t="shared" si="6"/>
         <v>-2196.0999999999995</v>
       </c>
       <c r="G424" t="str">
@@ -17917,7 +17900,7 @@
         <v>7754.2</v>
       </c>
       <c r="F425" s="7">
-        <f>E425-D425</f>
+        <f t="shared" si="6"/>
         <v>-4177.5000000000009</v>
       </c>
       <c r="G425" t="str">
@@ -17946,7 +17929,7 @@
         <v>14205.3</v>
       </c>
       <c r="F426" s="7">
-        <f>E426-D426</f>
+        <f t="shared" si="6"/>
         <v>3191</v>
       </c>
       <c r="G426" t="str">
@@ -17975,7 +17958,7 @@
         <v>10011.9</v>
       </c>
       <c r="F427" s="7">
-        <f>E427-D427</f>
+        <f t="shared" si="6"/>
         <v>1431.6999999999989</v>
       </c>
       <c r="G427" t="str">
@@ -18004,7 +17987,7 @@
         <v>77088.3</v>
       </c>
       <c r="F428" s="7">
-        <f>E428-D428</f>
+        <f t="shared" si="6"/>
         <v>35481</v>
       </c>
       <c r="G428" t="str">
@@ -18033,7 +18016,7 @@
         <v>98977.600000000006</v>
       </c>
       <c r="F429" s="7">
-        <f>E429-D429</f>
+        <f t="shared" si="6"/>
         <v>60680.000000000007</v>
       </c>
       <c r="G429" t="str">
@@ -18062,7 +18045,7 @@
         <v>79466.600000000006</v>
       </c>
       <c r="F430" s="7">
-        <f>E430-D430</f>
+        <f t="shared" si="6"/>
         <v>55419.100000000006</v>
       </c>
       <c r="G430" t="str">
@@ -18091,7 +18074,7 @@
         <v>54633.8</v>
       </c>
       <c r="F431" s="7">
-        <f>E431-D431</f>
+        <f t="shared" si="6"/>
         <v>17932</v>
       </c>
       <c r="G431" t="str">
@@ -18120,7 +18103,7 @@
         <v>30242.400000000001</v>
       </c>
       <c r="F432" s="7">
-        <f>E432-D432</f>
+        <f t="shared" si="6"/>
         <v>-1280</v>
       </c>
       <c r="G432" t="str">
@@ -18149,7 +18132,7 @@
         <v>42182.7</v>
       </c>
       <c r="F433" s="7">
-        <f>E433-D433</f>
+        <f t="shared" si="6"/>
         <v>19670.599999999999</v>
       </c>
       <c r="G433" t="str">
@@ -18178,7 +18161,7 @@
         <v>37911.599999999999</v>
       </c>
       <c r="F434" s="7">
-        <f>E434-D434</f>
+        <f t="shared" si="6"/>
         <v>10011.899999999998</v>
       </c>
       <c r="G434" t="str">
@@ -18207,7 +18190,7 @@
         <v>21839.599999999999</v>
       </c>
       <c r="F435" s="7">
-        <f>E435-D435</f>
+        <f t="shared" si="6"/>
         <v>-724.60000000000218</v>
       </c>
       <c r="G435" t="str">
@@ -18236,7 +18219,7 @@
         <v>55817.8</v>
       </c>
       <c r="F436" s="7">
-        <f>E436-D436</f>
+        <f t="shared" si="6"/>
         <v>34866.100000000006</v>
       </c>
       <c r="G436" t="str">
@@ -18265,7 +18248,7 @@
         <v>40396.300000000003</v>
       </c>
       <c r="F437" s="7">
-        <f>E437-D437</f>
+        <f t="shared" si="6"/>
         <v>21849.4</v>
       </c>
       <c r="G437" t="str">
@@ -18294,7 +18277,7 @@
         <v>36569.699999999997</v>
       </c>
       <c r="F438" s="10">
-        <f>E438-D438</f>
+        <f t="shared" si="6"/>
         <v>-35924.300000000003</v>
       </c>
       <c r="G438" t="str">
@@ -18323,7 +18306,7 @@
         <v>39461.1</v>
       </c>
       <c r="F439" s="10">
-        <f>E439-D439</f>
+        <f t="shared" si="6"/>
         <v>-39894.6</v>
       </c>
       <c r="G439" t="str">
@@ -18352,7 +18335,7 @@
         <v>38846.1</v>
       </c>
       <c r="F440" s="10">
-        <f>E440-D440</f>
+        <f t="shared" si="6"/>
         <v>-41699.000000000007</v>
       </c>
       <c r="G440" t="str">
@@ -18381,7 +18364,7 @@
         <v>36873.199999999997</v>
       </c>
       <c r="F441" s="10">
-        <f>E441-D441</f>
+        <f t="shared" si="6"/>
         <v>-25170.800000000003</v>
       </c>
       <c r="G441" t="str">
@@ -18410,7 +18393,7 @@
         <v>34357.199999999997</v>
       </c>
       <c r="F442" s="10">
-        <f>E442-D442</f>
+        <f t="shared" si="6"/>
         <v>-28436.700000000004</v>
       </c>
       <c r="G442" t="str">
@@ -18439,7 +18422,7 @@
         <v>36357.9</v>
       </c>
       <c r="F443" s="10">
-        <f>E443-D443</f>
+        <f t="shared" si="6"/>
         <v>-42711.999999999993</v>
       </c>
       <c r="G443" t="str">
@@ -18468,7 +18451,7 @@
         <v>28020.799999999999</v>
       </c>
       <c r="F444" s="10">
-        <f>E444-D444</f>
+        <f t="shared" si="6"/>
         <v>-42047.099999999991</v>
       </c>
       <c r="G444" t="str">
@@ -18497,7 +18480,7 @@
         <v>27264.799999999999</v>
       </c>
       <c r="F445" s="10">
-        <f>E445-D445</f>
+        <f t="shared" si="6"/>
         <v>-30711.399999999998</v>
       </c>
       <c r="G445" t="str">
@@ -18526,7 +18509,7 @@
         <v>32030.400000000001</v>
       </c>
       <c r="F446" s="10">
-        <f>E446-D446</f>
+        <f t="shared" si="6"/>
         <v>-24005</v>
       </c>
       <c r="G446" t="str">
@@ -18555,7 +18538,7 @@
         <v>28536.2</v>
       </c>
       <c r="F447" s="10">
-        <f>E447-D447</f>
+        <f t="shared" si="6"/>
         <v>3314.9000000000015</v>
       </c>
       <c r="G447" t="str">
@@ -18584,7 +18567,7 @@
         <v>1303.0999999999999</v>
       </c>
       <c r="F448" s="7">
-        <f>E448-D448</f>
+        <f t="shared" si="6"/>
         <v>-33575</v>
       </c>
       <c r="G448" t="str">
@@ -18613,7 +18596,7 @@
         <v>767.3</v>
       </c>
       <c r="F449" s="7">
-        <f>E449-D449</f>
+        <f t="shared" si="6"/>
         <v>-34779</v>
       </c>
       <c r="G449" t="str">
@@ -18642,7 +18625,7 @@
         <v>1536.3</v>
       </c>
       <c r="F450" s="7">
-        <f>E450-D450</f>
+        <f t="shared" ref="F450:F513" si="7">E450-D450</f>
         <v>-39384.899999999994</v>
       </c>
       <c r="G450" t="str">
@@ -18671,7 +18654,7 @@
         <v>1620.1</v>
       </c>
       <c r="F451" s="7">
-        <f>E451-D451</f>
+        <f t="shared" si="7"/>
         <v>-46284.1</v>
       </c>
       <c r="G451" t="str">
@@ -18700,7 +18683,7 @@
         <v>3098.4</v>
       </c>
       <c r="F452" s="7">
-        <f>E452-D452</f>
+        <f t="shared" si="7"/>
         <v>-39800.9</v>
       </c>
       <c r="G452" t="str">
@@ -18729,7 +18712,7 @@
         <v>3848.4</v>
       </c>
       <c r="F453" s="7">
-        <f>E453-D453</f>
+        <f t="shared" si="7"/>
         <v>-32350.9</v>
       </c>
       <c r="G453" t="str">
@@ -18758,7 +18741,7 @@
         <v>6527.4</v>
       </c>
       <c r="F454" s="7">
-        <f>E454-D454</f>
+        <f t="shared" si="7"/>
         <v>-27437.599999999999</v>
       </c>
       <c r="G454" t="str">
@@ -18787,7 +18770,7 @@
         <v>4228.6000000000004</v>
       </c>
       <c r="F455" s="7">
-        <f>E455-D455</f>
+        <f t="shared" si="7"/>
         <v>-34796.400000000001</v>
       </c>
       <c r="G455" t="str">
@@ -18816,7 +18799,7 @@
         <v>4180.2</v>
       </c>
       <c r="F456" s="7">
-        <f>E456-D456</f>
+        <f t="shared" si="7"/>
         <v>-35004.600000000006</v>
       </c>
       <c r="G456" t="str">
@@ -18845,7 +18828,7 @@
         <v>3628</v>
       </c>
       <c r="F457" s="7">
-        <f>E457-D457</f>
+        <f t="shared" si="7"/>
         <v>-33875.5</v>
       </c>
       <c r="G457" t="str">
@@ -18874,7 +18857,7 @@
         <v>86</v>
       </c>
       <c r="F458" s="7">
-        <f>E458-D458</f>
+        <f t="shared" si="7"/>
         <v>-182537</v>
       </c>
       <c r="G458" t="str">
@@ -18903,7 +18886,7 @@
         <v>109.7</v>
       </c>
       <c r="F459" s="7">
-        <f>E459-D459</f>
+        <f t="shared" si="7"/>
         <v>-168560.8</v>
       </c>
       <c r="G459" t="str">
@@ -18932,7 +18915,7 @@
         <v>283.8</v>
       </c>
       <c r="F460" s="7">
-        <f>E460-D460</f>
+        <f t="shared" si="7"/>
         <v>-177631.6</v>
       </c>
       <c r="G460" t="str">
@@ -18961,7 +18944,7 @@
         <v>1098.5</v>
       </c>
       <c r="F461" s="7">
-        <f>E461-D461</f>
+        <f t="shared" si="7"/>
         <v>-183293.2</v>
       </c>
       <c r="G461" t="str">
@@ -18990,7 +18973,7 @@
         <v>15.6</v>
       </c>
       <c r="F462" s="7">
-        <f>E462-D462</f>
+        <f t="shared" si="7"/>
         <v>-187000</v>
       </c>
       <c r="G462" t="str">
@@ -19019,7 +19002,7 @@
         <v>34</v>
       </c>
       <c r="F463" s="7">
-        <f>E463-D463</f>
+        <f t="shared" si="7"/>
         <v>-169389.7</v>
       </c>
       <c r="G463" t="str">
@@ -19048,7 +19031,7 @@
         <v>20.8</v>
       </c>
       <c r="F464" s="7">
-        <f>E464-D464</f>
+        <f t="shared" si="7"/>
         <v>-165003.20000000001</v>
       </c>
       <c r="G464" t="str">
@@ -19077,7 +19060,7 @@
         <v>986.9</v>
       </c>
       <c r="F465" s="7">
-        <f>E465-D465</f>
+        <f t="shared" si="7"/>
         <v>-110521.70000000001</v>
       </c>
       <c r="G465" t="str">
@@ -19106,7 +19089,7 @@
         <v>2598.1999999999998</v>
       </c>
       <c r="F466" s="7">
-        <f>E466-D466</f>
+        <f t="shared" si="7"/>
         <v>-99298</v>
       </c>
       <c r="G466" t="str">
@@ -19135,7 +19118,7 @@
         <v>2650.8</v>
       </c>
       <c r="F467" s="7">
-        <f>E467-D467</f>
+        <f t="shared" si="7"/>
         <v>-88025.3</v>
       </c>
       <c r="G467" t="str">
@@ -19164,7 +19147,7 @@
         <v>1167.2</v>
       </c>
       <c r="F468" s="7">
-        <f>E468-D468</f>
+        <f t="shared" si="7"/>
         <v>-1775150.8</v>
       </c>
       <c r="G468" t="str">
@@ -19193,7 +19176,7 @@
         <v>323.89999999999998</v>
       </c>
       <c r="F469" s="7">
-        <f>E469-D469</f>
+        <f t="shared" si="7"/>
         <v>-1939247.8</v>
       </c>
       <c r="G469" t="str">
@@ -19222,7 +19205,7 @@
         <v>0</v>
       </c>
       <c r="F470" s="7">
-        <f>E470-D470</f>
+        <f t="shared" si="7"/>
         <v>-1745184.3</v>
       </c>
       <c r="G470" t="str">
@@ -19251,7 +19234,7 @@
         <v>86.6</v>
       </c>
       <c r="F471" s="7">
-        <f>E471-D471</f>
+        <f t="shared" si="7"/>
         <v>-2030499.5999999999</v>
       </c>
       <c r="G471" t="str">
@@ -19280,7 +19263,7 @@
         <v>620.9</v>
       </c>
       <c r="F472" s="7">
-        <f>E472-D472</f>
+        <f t="shared" si="7"/>
         <v>-1949729</v>
       </c>
       <c r="G472" t="str">
@@ -19309,7 +19292,7 @@
         <v>176.2</v>
       </c>
       <c r="F473" s="7">
-        <f>E473-D473</f>
+        <f t="shared" si="7"/>
         <v>-1412357.9000000001</v>
       </c>
       <c r="G473" t="str">
@@ -19338,7 +19321,7 @@
         <v>230.2</v>
       </c>
       <c r="F474" s="7">
-        <f>E474-D474</f>
+        <f t="shared" si="7"/>
         <v>-1645976.7</v>
       </c>
       <c r="G474" t="str">
@@ -19367,7 +19350,7 @@
         <v>637.6</v>
       </c>
       <c r="F475" s="7">
-        <f>E475-D475</f>
+        <f t="shared" si="7"/>
         <v>-2087724.5999999999</v>
       </c>
       <c r="G475" t="str">
@@ -19396,7 +19379,7 @@
         <v>975.6</v>
       </c>
       <c r="F476" s="7">
-        <f>E476-D476</f>
+        <f t="shared" si="7"/>
         <v>-2197289.5</v>
       </c>
       <c r="G476" t="str">
@@ -19425,7 +19408,7 @@
         <v>2592.8000000000002</v>
       </c>
       <c r="F477" s="7">
-        <f>E477-D477</f>
+        <f t="shared" si="7"/>
         <v>-1997144</v>
       </c>
       <c r="G477" t="str">
@@ -19454,7 +19437,7 @@
         <v>167.7</v>
       </c>
       <c r="F478" s="7">
-        <f>E478-D478</f>
+        <f t="shared" si="7"/>
         <v>-37103</v>
       </c>
       <c r="G478" t="str">
@@ -19483,7 +19466,7 @@
         <v>287</v>
       </c>
       <c r="F479" s="7">
-        <f>E479-D479</f>
+        <f t="shared" si="7"/>
         <v>-49193.5</v>
       </c>
       <c r="G479" t="str">
@@ -19512,7 +19495,7 @@
         <v>144.19999999999999</v>
       </c>
       <c r="F480" s="7">
-        <f>E480-D480</f>
+        <f t="shared" si="7"/>
         <v>-44132.700000000004</v>
       </c>
       <c r="G480" t="str">
@@ -19541,7 +19524,7 @@
         <v>393.7</v>
       </c>
       <c r="F481" s="7">
-        <f>E481-D481</f>
+        <f t="shared" si="7"/>
         <v>-40088.5</v>
       </c>
       <c r="G481" t="str">
@@ -19570,7 +19553,7 @@
         <v>373.8</v>
       </c>
       <c r="F482" s="7">
-        <f>E482-D482</f>
+        <f t="shared" si="7"/>
         <v>-39246.199999999997</v>
       </c>
       <c r="G482" t="str">
@@ -19599,7 +19582,7 @@
         <v>359.7</v>
       </c>
       <c r="F483" s="7">
-        <f>E483-D483</f>
+        <f t="shared" si="7"/>
         <v>-45494.600000000006</v>
       </c>
       <c r="G483" t="str">
@@ -19628,7 +19611,7 @@
         <v>154.1</v>
       </c>
       <c r="F484" s="7">
-        <f>E484-D484</f>
+        <f t="shared" si="7"/>
         <v>-43494.9</v>
       </c>
       <c r="G484" t="str">
@@ -19657,7 +19640,7 @@
         <v>933.9</v>
       </c>
       <c r="F485" s="7">
-        <f>E485-D485</f>
+        <f t="shared" si="7"/>
         <v>-53426.1</v>
       </c>
       <c r="G485" t="str">
@@ -19686,7 +19669,7 @@
         <v>430.3</v>
       </c>
       <c r="F486" s="7">
-        <f>E486-D486</f>
+        <f t="shared" si="7"/>
         <v>-52355.399999999994</v>
       </c>
       <c r="G486" t="str">
@@ -19715,7 +19698,7 @@
         <v>0.1</v>
       </c>
       <c r="F487" s="7">
-        <f>E487-D487</f>
+        <f t="shared" si="7"/>
         <v>-56296.5</v>
       </c>
       <c r="G487" t="str">
@@ -19744,7 +19727,7 @@
         <v>16224.2</v>
       </c>
       <c r="F488" s="7">
-        <f>E488-D488</f>
+        <f t="shared" si="7"/>
         <v>14431.6</v>
       </c>
       <c r="G488" t="str">
@@ -19773,7 +19756,7 @@
         <v>17349.900000000001</v>
       </c>
       <c r="F489" s="7">
-        <f>E489-D489</f>
+        <f t="shared" si="7"/>
         <v>13713.100000000002</v>
       </c>
       <c r="G489" t="str">
@@ -19802,7 +19785,7 @@
         <v>125.3</v>
       </c>
       <c r="F490" s="7">
-        <f>E490-D490</f>
+        <f t="shared" si="7"/>
         <v>-4421.5999999999995</v>
       </c>
       <c r="G490" t="str">
@@ -19831,7 +19814,7 @@
         <v>167.2</v>
       </c>
       <c r="F491" s="7">
-        <f>E491-D491</f>
+        <f t="shared" si="7"/>
         <v>-1923.3</v>
       </c>
       <c r="G491" t="str">
@@ -19860,7 +19843,7 @@
         <v>4243.2</v>
       </c>
       <c r="F492" s="7">
-        <f>E492-D492</f>
+        <f t="shared" si="7"/>
         <v>2373.6999999999998</v>
       </c>
       <c r="G492" t="str">
@@ -19889,7 +19872,7 @@
         <v>9977.7000000000007</v>
       </c>
       <c r="F493" s="7">
-        <f>E493-D493</f>
+        <f t="shared" si="7"/>
         <v>9287.9000000000015</v>
       </c>
       <c r="G493" t="str">
@@ -19918,7 +19901,7 @@
         <v>7239.4</v>
       </c>
       <c r="F494" s="7">
-        <f>E494-D494</f>
+        <f t="shared" si="7"/>
         <v>6970.4</v>
       </c>
       <c r="G494" t="str">
@@ -19947,7 +19930,7 @@
         <v>3300</v>
       </c>
       <c r="F495" s="7">
-        <f>E495-D495</f>
+        <f t="shared" si="7"/>
         <v>3209.6</v>
       </c>
       <c r="G495" t="str">
@@ -19976,7 +19959,7 @@
         <v>15209</v>
       </c>
       <c r="F496" s="7">
-        <f>E496-D496</f>
+        <f t="shared" si="7"/>
         <v>15208.9</v>
       </c>
       <c r="G496" t="str">
@@ -20005,7 +19988,7 @@
         <v>5786.2</v>
       </c>
       <c r="F497" s="7">
-        <f>E497-D497</f>
+        <f t="shared" si="7"/>
         <v>3800.3999999999996</v>
       </c>
       <c r="G497" t="str">
@@ -20034,7 +20017,7 @@
         <v>3728.2</v>
       </c>
       <c r="F498" s="7">
-        <f>E498-D498</f>
+        <f t="shared" si="7"/>
         <v>2294.6999999999998</v>
       </c>
       <c r="G498" t="str">
@@ -20063,7 +20046,7 @@
         <v>4901.6000000000004</v>
       </c>
       <c r="F499" s="7">
-        <f>E499-D499</f>
+        <f t="shared" si="7"/>
         <v>4472.6000000000004</v>
       </c>
       <c r="G499" t="str">
@@ -20092,7 +20075,7 @@
         <v>5274.3</v>
       </c>
       <c r="F500" s="7">
-        <f>E500-D500</f>
+        <f t="shared" si="7"/>
         <v>5168</v>
       </c>
       <c r="G500" t="str">
@@ -20121,7 +20104,7 @@
         <v>6934.8</v>
       </c>
       <c r="F501" s="7">
-        <f>E501-D501</f>
+        <f t="shared" si="7"/>
         <v>6588.4000000000005</v>
       </c>
       <c r="G501" t="str">
@@ -20150,7 +20133,7 @@
         <v>6578.3</v>
       </c>
       <c r="F502" s="7">
-        <f>E502-D502</f>
+        <f t="shared" si="7"/>
         <v>5982.9000000000005</v>
       </c>
       <c r="G502" t="str">
@@ -20179,7 +20162,7 @@
         <v>7180.1</v>
       </c>
       <c r="F503" s="7">
-        <f>E503-D503</f>
+        <f t="shared" si="7"/>
         <v>6503.5</v>
       </c>
       <c r="G503" t="str">
@@ -20208,7 +20191,7 @@
         <v>9073.7999999999993</v>
       </c>
       <c r="F504" s="7">
-        <f>E504-D504</f>
+        <f t="shared" si="7"/>
         <v>8097.7999999999993</v>
       </c>
       <c r="G504" t="str">
@@ -20237,7 +20220,7 @@
         <v>6580.8</v>
       </c>
       <c r="F505" s="7">
-        <f>E505-D505</f>
+        <f t="shared" si="7"/>
         <v>4571.1000000000004</v>
       </c>
       <c r="G505" t="str">
@@ -20266,7 +20249,7 @@
         <v>7347.1</v>
       </c>
       <c r="F506" s="7">
-        <f>E506-D506</f>
+        <f t="shared" si="7"/>
         <v>5655</v>
       </c>
       <c r="G506" t="str">
@@ -20295,7 +20278,7 @@
         <v>8056.1</v>
       </c>
       <c r="F507" s="7">
-        <f>E507-D507</f>
+        <f t="shared" si="7"/>
         <v>6906</v>
       </c>
       <c r="G507" t="str">
@@ -20324,7 +20307,7 @@
         <v>2481.8000000000002</v>
       </c>
       <c r="F508" s="7">
-        <f>E508-D508</f>
+        <f t="shared" si="7"/>
         <v>1669.3000000000002</v>
       </c>
       <c r="G508" t="str">
@@ -20353,7 +20336,7 @@
         <v>2513</v>
       </c>
       <c r="F509" s="7">
-        <f>E509-D509</f>
+        <f t="shared" si="7"/>
         <v>2070.9</v>
       </c>
       <c r="G509" t="str">
@@ -20382,7 +20365,7 @@
         <v>2800.3</v>
       </c>
       <c r="F510" s="7">
-        <f>E510-D510</f>
+        <f t="shared" si="7"/>
         <v>2571.9</v>
       </c>
       <c r="G510" t="str">
@@ -20411,7 +20394,7 @@
         <v>3476</v>
       </c>
       <c r="F511" s="7">
-        <f>E511-D511</f>
+        <f t="shared" si="7"/>
         <v>3144.1</v>
       </c>
       <c r="G511" t="str">
@@ -20440,7 +20423,7 @@
         <v>3223.4</v>
       </c>
       <c r="F512" s="7">
-        <f>E512-D512</f>
+        <f t="shared" si="7"/>
         <v>1984.4</v>
       </c>
       <c r="G512" t="str">
@@ -20469,7 +20452,7 @@
         <v>3971.7</v>
       </c>
       <c r="F513" s="7">
-        <f>E513-D513</f>
+        <f t="shared" si="7"/>
         <v>2817</v>
       </c>
       <c r="G513" t="str">
@@ -20498,7 +20481,7 @@
         <v>3139.9</v>
       </c>
       <c r="F514" s="7">
-        <f>E514-D514</f>
+        <f t="shared" ref="F514:F577" si="8">E514-D514</f>
         <v>2376</v>
       </c>
       <c r="G514" t="str">
@@ -20527,7 +20510,7 @@
         <v>4850.7</v>
       </c>
       <c r="F515" s="7">
-        <f>E515-D515</f>
+        <f t="shared" si="8"/>
         <v>4025.5</v>
       </c>
       <c r="G515" t="str">
@@ -20556,7 +20539,7 @@
         <v>3891.1</v>
       </c>
       <c r="F516" s="7">
-        <f>E516-D516</f>
+        <f t="shared" si="8"/>
         <v>2550.3000000000002</v>
       </c>
       <c r="G516" t="str">
@@ -20585,7 +20568,7 @@
         <v>3625.5</v>
       </c>
       <c r="F517" s="7">
-        <f>E517-D517</f>
+        <f t="shared" si="8"/>
         <v>2879.2</v>
       </c>
       <c r="G517" t="str">
@@ -20614,7 +20597,7 @@
         <v>7909.9</v>
       </c>
       <c r="F518" s="7">
-        <f>E518-D518</f>
+        <f t="shared" si="8"/>
         <v>6799.9</v>
       </c>
       <c r="G518" t="str">
@@ -20643,7 +20626,7 @@
         <v>7557.1</v>
       </c>
       <c r="F519" s="7">
-        <f>E519-D519</f>
+        <f t="shared" si="8"/>
         <v>6644</v>
       </c>
       <c r="G519" t="str">
@@ -20672,7 +20655,7 @@
         <v>9925.2000000000007</v>
       </c>
       <c r="F520" s="7">
-        <f>E520-D520</f>
+        <f t="shared" si="8"/>
         <v>9207</v>
       </c>
       <c r="G520" t="str">
@@ -20701,7 +20684,7 @@
         <v>9098.5</v>
       </c>
       <c r="F521" s="7">
-        <f>E521-D521</f>
+        <f t="shared" si="8"/>
         <v>7695.6</v>
       </c>
       <c r="G521" t="str">
@@ -20730,7 +20713,7 @@
         <v>9986.7999999999993</v>
       </c>
       <c r="F522" s="7">
-        <f>E522-D522</f>
+        <f t="shared" si="8"/>
         <v>8322.0999999999985</v>
       </c>
       <c r="G522" t="str">
@@ -20759,7 +20742,7 @@
         <v>9570.7000000000007</v>
       </c>
       <c r="F523" s="7">
-        <f>E523-D523</f>
+        <f t="shared" si="8"/>
         <v>7970.0000000000009</v>
       </c>
       <c r="G523" t="str">
@@ -20788,7 +20771,7 @@
         <v>10525.8</v>
       </c>
       <c r="F524" s="7">
-        <f>E524-D524</f>
+        <f t="shared" si="8"/>
         <v>8966.7999999999993</v>
       </c>
       <c r="G524" t="str">
@@ -20817,7 +20800,7 @@
         <v>10779.6</v>
       </c>
       <c r="F525" s="7">
-        <f>E525-D525</f>
+        <f t="shared" si="8"/>
         <v>8015.8</v>
       </c>
       <c r="G525" t="str">
@@ -20846,7 +20829,7 @@
         <v>12068.7</v>
       </c>
       <c r="F526" s="7">
-        <f>E526-D526</f>
+        <f t="shared" si="8"/>
         <v>9670.6</v>
       </c>
       <c r="G526" t="str">
@@ -20875,7 +20858,7 @@
         <v>134577.4</v>
       </c>
       <c r="F527" s="7">
-        <f>E527-D527</f>
+        <f t="shared" si="8"/>
         <v>-106331.4</v>
       </c>
       <c r="G527" t="str">
@@ -20904,7 +20887,7 @@
         <v>150867.5</v>
       </c>
       <c r="F528" s="7">
-        <f>E528-D528</f>
+        <f t="shared" si="8"/>
         <v>-119724.90000000002</v>
       </c>
       <c r="G528" t="str">
@@ -20933,7 +20916,7 @@
         <v>169131.8</v>
       </c>
       <c r="F529" s="7">
-        <f>E529-D529</f>
+        <f t="shared" si="8"/>
         <v>-62344.600000000006</v>
       </c>
       <c r="G529" t="str">
@@ -20962,7 +20945,7 @@
         <v>165629</v>
       </c>
       <c r="F530" s="7">
-        <f>E530-D530</f>
+        <f t="shared" si="8"/>
         <v>-83284.299999999988</v>
       </c>
       <c r="G530" t="str">
@@ -20991,7 +20974,7 @@
         <v>187214</v>
       </c>
       <c r="F531" s="7">
-        <f>E531-D531</f>
+        <f t="shared" si="8"/>
         <v>-17075.299999999988</v>
       </c>
       <c r="G531" t="str">
@@ -21020,7 +21003,7 @@
         <v>216038.7</v>
       </c>
       <c r="F532" s="7">
-        <f>E532-D532</f>
+        <f t="shared" si="8"/>
         <v>-46043.199999999983</v>
       </c>
       <c r="G532" t="str">
@@ -21049,7 +21032,7 @@
         <v>173566.5</v>
       </c>
       <c r="F533" s="7">
-        <f>E533-D533</f>
+        <f t="shared" si="8"/>
         <v>-61922.100000000006</v>
       </c>
       <c r="G533" t="str">
@@ -21078,7 +21061,7 @@
         <v>167596.4</v>
       </c>
       <c r="F534" s="7">
-        <f>E534-D534</f>
+        <f t="shared" si="8"/>
         <v>-25499.399999999994</v>
       </c>
       <c r="G534" t="str">
@@ -21107,7 +21090,7 @@
         <v>184601.7</v>
       </c>
       <c r="F535" s="7">
-        <f>E535-D535</f>
+        <f t="shared" si="8"/>
         <v>8685.7000000000116</v>
       </c>
       <c r="G535" t="str">
@@ -21136,7 +21119,7 @@
         <v>213741.3</v>
       </c>
       <c r="F536" s="7">
-        <f>E536-D536</f>
+        <f t="shared" si="8"/>
         <v>-60281.600000000035</v>
       </c>
       <c r="G536" t="str">
@@ -21165,7 +21148,7 @@
         <v>1722.2</v>
       </c>
       <c r="F537" s="7">
-        <f>E537-D537</f>
+        <f t="shared" si="8"/>
         <v>-263094.5</v>
       </c>
       <c r="G537" t="str">
@@ -21194,7 +21177,7 @@
         <v>534.20000000000005</v>
       </c>
       <c r="F538" s="7">
-        <f>E538-D538</f>
+        <f t="shared" si="8"/>
         <v>-297392.59999999998</v>
       </c>
       <c r="G538" t="str">
@@ -21223,7 +21206,7 @@
         <v>2525.6999999999998</v>
       </c>
       <c r="F539" s="7">
-        <f>E539-D539</f>
+        <f t="shared" si="8"/>
         <v>-272075.59999999998</v>
       </c>
       <c r="G539" t="str">
@@ -21252,7 +21235,7 @@
         <v>7004.7</v>
       </c>
       <c r="F540" s="7">
-        <f>E540-D540</f>
+        <f t="shared" si="8"/>
         <v>-245730.3</v>
       </c>
       <c r="G540" t="str">
@@ -21281,7 +21264,7 @@
         <v>2706.1</v>
       </c>
       <c r="F541" s="7">
-        <f>E541-D541</f>
+        <f t="shared" si="8"/>
         <v>-208479.3</v>
       </c>
       <c r="G541" t="str">
@@ -21310,7 +21293,7 @@
         <v>2153.1</v>
       </c>
       <c r="F542" s="7">
-        <f>E542-D542</f>
+        <f t="shared" si="8"/>
         <v>-231107.8</v>
       </c>
       <c r="G542" t="str">
@@ -21339,7 +21322,7 @@
         <v>1493.7</v>
       </c>
       <c r="F543" s="7">
-        <f>E543-D543</f>
+        <f t="shared" si="8"/>
         <v>-245996.09999999998</v>
       </c>
       <c r="G543" t="str">
@@ -21368,7 +21351,7 @@
         <v>2312.3000000000002</v>
       </c>
       <c r="F544" s="7">
-        <f>E544-D544</f>
+        <f t="shared" si="8"/>
         <v>-294658.60000000003</v>
       </c>
       <c r="G544" t="str">
@@ -21397,7 +21380,7 @@
         <v>2306.5</v>
       </c>
       <c r="F545" s="7">
-        <f>E545-D545</f>
+        <f t="shared" si="8"/>
         <v>-298567.59999999998</v>
       </c>
       <c r="G545" t="str">
@@ -21426,7 +21409,7 @@
         <v>2725.5</v>
       </c>
       <c r="F546" s="7">
-        <f>E546-D546</f>
+        <f t="shared" si="8"/>
         <v>-270937.7</v>
       </c>
       <c r="G546" t="str">
@@ -21455,7 +21438,7 @@
         <v>1427.4</v>
       </c>
       <c r="F547" s="7">
-        <f>E547-D547</f>
+        <f t="shared" si="8"/>
         <v>-61133.599999999999</v>
       </c>
       <c r="G547" t="str">
@@ -21484,7 +21467,7 @@
         <v>1679.4</v>
       </c>
       <c r="F548" s="7">
-        <f>E548-D548</f>
+        <f t="shared" si="8"/>
         <v>-57362.799999999996</v>
       </c>
       <c r="G548" t="str">
@@ -21513,7 +21496,7 @@
         <v>2189.6</v>
       </c>
       <c r="F549" s="7">
-        <f>E549-D549</f>
+        <f t="shared" si="8"/>
         <v>-82221.399999999994</v>
       </c>
       <c r="G549" t="str">
@@ -21542,7 +21525,7 @@
         <v>2046</v>
       </c>
       <c r="F550" s="7">
-        <f>E550-D550</f>
+        <f t="shared" si="8"/>
         <v>-87493.2</v>
       </c>
       <c r="G550" t="str">
@@ -21571,7 +21554,7 @@
         <v>2150.1999999999998</v>
       </c>
       <c r="F551" s="7">
-        <f>E551-D551</f>
+        <f t="shared" si="8"/>
         <v>-93894.7</v>
       </c>
       <c r="G551" t="str">
@@ -21600,7 +21583,7 @@
         <v>1494.9</v>
       </c>
       <c r="F552" s="7">
-        <f>E552-D552</f>
+        <f t="shared" si="8"/>
         <v>-100249.8</v>
       </c>
       <c r="G552" t="str">
@@ -21629,7 +21612,7 @@
         <v>1612.9</v>
       </c>
       <c r="F553" s="7">
-        <f>E553-D553</f>
+        <f t="shared" si="8"/>
         <v>-94108.3</v>
       </c>
       <c r="G553" t="str">
@@ -21658,7 +21641,7 @@
         <v>1429.8</v>
       </c>
       <c r="F554" s="7">
-        <f>E554-D554</f>
+        <f t="shared" si="8"/>
         <v>-108674.2</v>
       </c>
       <c r="G554" t="str">
@@ -21687,7 +21670,7 @@
         <v>1672.6</v>
       </c>
       <c r="F555" s="7">
-        <f>E555-D555</f>
+        <f t="shared" si="8"/>
         <v>-130920.19999999998</v>
       </c>
       <c r="G555" t="str">
@@ -21716,7 +21699,7 @@
         <v>1458.2</v>
       </c>
       <c r="F556" s="7">
-        <f>E556-D556</f>
+        <f t="shared" si="8"/>
         <v>-155515.29999999999</v>
       </c>
       <c r="G556" t="str">
@@ -21745,7 +21728,7 @@
         <v>35903.599999999999</v>
       </c>
       <c r="F557" s="7">
-        <f>E557-D557</f>
+        <f t="shared" si="8"/>
         <v>-1361.4000000000015</v>
       </c>
       <c r="G557" t="str">
@@ -21774,7 +21757,7 @@
         <v>26417.5</v>
       </c>
       <c r="F558" s="7">
-        <f>E558-D558</f>
+        <f t="shared" si="8"/>
         <v>-25363.599999999999</v>
       </c>
       <c r="G558" t="str">
@@ -21803,7 +21786,7 @@
         <v>16638.3</v>
       </c>
       <c r="F559" s="7">
-        <f>E559-D559</f>
+        <f t="shared" si="8"/>
         <v>-21617.7</v>
       </c>
       <c r="G559" t="str">
@@ -21832,7 +21815,7 @@
         <v>22217.8</v>
       </c>
       <c r="F560" s="7">
-        <f>E560-D560</f>
+        <f t="shared" si="8"/>
         <v>-21517.600000000002</v>
       </c>
       <c r="G560" t="str">
@@ -21861,7 +21844,7 @@
         <v>22287.599999999999</v>
       </c>
       <c r="F561" s="13">
-        <f>E561-D561</f>
+        <f t="shared" si="8"/>
         <v>-24033.4</v>
       </c>
       <c r="G561" t="str">
@@ -21890,7 +21873,7 @@
         <v>19447.7</v>
       </c>
       <c r="F562" s="13">
-        <f>E562-D562</f>
+        <f t="shared" si="8"/>
         <v>-21977.3</v>
       </c>
       <c r="G562" t="str">
@@ -21919,7 +21902,7 @@
         <v>28995</v>
       </c>
       <c r="F563" s="13">
-        <f>E563-D563</f>
+        <f t="shared" si="8"/>
         <v>14206</v>
       </c>
       <c r="G563" t="str">
@@ -21948,7 +21931,7 @@
         <v>42076.3</v>
       </c>
       <c r="F564" s="13">
-        <f>E564-D564</f>
+        <f t="shared" si="8"/>
         <v>42028.3</v>
       </c>
       <c r="G564" t="str">
@@ -21977,7 +21960,7 @@
         <v>16528.5</v>
       </c>
       <c r="F565" s="14">
-        <f>E565-D565</f>
+        <f t="shared" si="8"/>
         <v>16494.5</v>
       </c>
       <c r="G565" t="str">
@@ -22006,7 +21989,7 @@
         <v>9068.2999999999993</v>
       </c>
       <c r="F566" s="7">
-        <f>E566-D566</f>
+        <f t="shared" si="8"/>
         <v>9068</v>
       </c>
       <c r="G566" t="str">
@@ -22035,7 +22018,7 @@
         <v>12545.3</v>
       </c>
       <c r="F567" s="7">
-        <f>E567-D567</f>
+        <f t="shared" si="8"/>
         <v>-539787.29999999993</v>
       </c>
       <c r="G567" t="str">
@@ -22064,7 +22047,7 @@
         <v>23654.799999999999</v>
       </c>
       <c r="F568" s="7">
-        <f>E568-D568</f>
+        <f t="shared" si="8"/>
         <v>-482053.4</v>
       </c>
       <c r="G568" t="str">
@@ -22093,7 +22076,7 @@
         <v>34465.599999999999</v>
       </c>
       <c r="F569" s="7">
-        <f>E569-D569</f>
+        <f t="shared" si="8"/>
         <v>-393031.80000000005</v>
       </c>
       <c r="G569" t="str">
@@ -22122,7 +22105,7 @@
         <v>50033.9</v>
       </c>
       <c r="F570" s="7">
-        <f>E570-D570</f>
+        <f t="shared" si="8"/>
         <v>-338289.3</v>
       </c>
       <c r="G570" t="str">
@@ -22151,7 +22134,7 @@
         <v>58581.2</v>
       </c>
       <c r="F571" s="7">
-        <f>E571-D571</f>
+        <f t="shared" si="8"/>
         <v>-220084.2</v>
       </c>
       <c r="G571" t="str">
@@ -22180,7 +22163,7 @@
         <v>37919.5</v>
       </c>
       <c r="F572" s="7">
-        <f>E572-D572</f>
+        <f t="shared" si="8"/>
         <v>-430253</v>
       </c>
       <c r="G572" t="str">
@@ -22209,7 +22192,7 @@
         <v>23887.8</v>
       </c>
       <c r="F573" s="7">
-        <f>E573-D573</f>
+        <f t="shared" si="8"/>
         <v>-315632.3</v>
       </c>
       <c r="G573" t="str">
@@ -22238,7 +22221,7 @@
         <v>36077.199999999997</v>
       </c>
       <c r="F574" s="7">
-        <f>E574-D574</f>
+        <f t="shared" si="8"/>
         <v>-247259.5</v>
       </c>
       <c r="G574" t="str">
@@ -22267,7 +22250,7 @@
         <v>34515.4</v>
       </c>
       <c r="F575" s="7">
-        <f>E575-D575</f>
+        <f t="shared" si="8"/>
         <v>-205406.5</v>
       </c>
       <c r="G575" t="str">
@@ -22296,7 +22279,7 @@
         <v>38144.800000000003</v>
       </c>
       <c r="F576" s="7">
-        <f>E576-D576</f>
+        <f t="shared" si="8"/>
         <v>-139215.5</v>
       </c>
       <c r="G576" t="str">
@@ -22325,7 +22308,7 @@
         <v>98862.1</v>
       </c>
       <c r="F577" s="10">
-        <f>E577-D577</f>
+        <f t="shared" si="8"/>
         <v>-303764.59999999998</v>
       </c>
       <c r="G577" t="str">
@@ -22354,7 +22337,7 @@
         <v>126079</v>
       </c>
       <c r="F578" s="10">
-        <f>E578-D578</f>
+        <f t="shared" ref="F578:F641" si="9">E578-D578</f>
         <v>-275435.59999999998</v>
       </c>
       <c r="G578" t="str">
@@ -22383,7 +22366,7 @@
         <v>129685.1</v>
       </c>
       <c r="F579" s="10">
-        <f>E579-D579</f>
+        <f t="shared" si="9"/>
         <v>-338324.9</v>
       </c>
       <c r="G579" t="str">
@@ -22412,7 +22395,7 @@
         <v>159805</v>
       </c>
       <c r="F580" s="10">
-        <f>E580-D580</f>
+        <f t="shared" si="9"/>
         <v>-253066.7</v>
       </c>
       <c r="G580" t="str">
@@ -22441,7 +22424,7 @@
         <v>138517.6</v>
       </c>
       <c r="F581" s="10">
-        <f>E581-D581</f>
+        <f t="shared" si="9"/>
         <v>-231881.30000000002</v>
       </c>
       <c r="G581" t="str">
@@ -22470,7 +22453,7 @@
         <v>142573.4</v>
       </c>
       <c r="F582" s="10">
-        <f>E582-D582</f>
+        <f t="shared" si="9"/>
         <v>-173267.69999999998</v>
       </c>
       <c r="G582" t="str">
@@ -22499,7 +22482,7 @@
         <v>102742.6</v>
       </c>
       <c r="F583" s="10">
-        <f>E583-D583</f>
+        <f t="shared" si="9"/>
         <v>-261918.80000000002</v>
       </c>
       <c r="G583" t="str">
@@ -22528,7 +22511,7 @@
         <v>121419.7</v>
       </c>
       <c r="F584" s="10">
-        <f>E584-D584</f>
+        <f t="shared" si="9"/>
         <v>-235334.09999999998</v>
       </c>
       <c r="G584" t="str">
@@ -22557,7 +22540,7 @@
         <v>97866.5</v>
       </c>
       <c r="F585" s="10">
-        <f>E585-D585</f>
+        <f t="shared" si="9"/>
         <v>-348992.2</v>
       </c>
       <c r="G585" t="str">
@@ -22586,7 +22569,7 @@
         <v>77880.600000000006</v>
       </c>
       <c r="F586" s="10">
-        <f>E586-D586</f>
+        <f t="shared" si="9"/>
         <v>-355674.1</v>
       </c>
       <c r="G586" t="str">
@@ -22614,8 +22597,8 @@
       <c r="E587" s="6">
         <v>14296.1</v>
       </c>
-      <c r="F587" s="16">
-        <f>E587-D587</f>
+      <c r="F587" s="7">
+        <f t="shared" si="9"/>
         <v>-1393994.9</v>
       </c>
       <c r="G587" t="str">
@@ -22643,8 +22626,8 @@
       <c r="E588" s="6">
         <v>18168.099999999999</v>
       </c>
-      <c r="F588" s="16">
-        <f>E588-D588</f>
+      <c r="F588" s="7">
+        <f t="shared" si="9"/>
         <v>-1621523.5999999999</v>
       </c>
       <c r="G588" t="str">
@@ -22672,8 +22655,8 @@
       <c r="E589" s="6">
         <v>18147.099999999999</v>
       </c>
-      <c r="F589" s="16">
-        <f>E589-D589</f>
+      <c r="F589" s="7">
+        <f t="shared" si="9"/>
         <v>-1722936.2999999998</v>
       </c>
       <c r="G589" t="str">
@@ -22701,8 +22684,8 @@
       <c r="E590" s="6">
         <v>19182.8</v>
       </c>
-      <c r="F590" s="16">
-        <f>E590-D590</f>
+      <c r="F590" s="7">
+        <f t="shared" si="9"/>
         <v>-1736814.9</v>
       </c>
       <c r="G590" t="str">
@@ -22730,8 +22713,8 @@
       <c r="E591" s="6">
         <v>12168.8</v>
       </c>
-      <c r="F591" s="16">
-        <f>E591-D591</f>
+      <c r="F591" s="7">
+        <f t="shared" si="9"/>
         <v>-1754916.4</v>
       </c>
       <c r="G591" t="str">
@@ -22760,7 +22743,7 @@
         <v>15319</v>
       </c>
       <c r="F592" s="7">
-        <f>E592-D592</f>
+        <f t="shared" si="9"/>
         <v>-2025372.3</v>
       </c>
       <c r="G592" t="str">
@@ -22789,7 +22772,7 @@
         <v>15108.5</v>
       </c>
       <c r="F593" s="7">
-        <f>E593-D593</f>
+        <f t="shared" si="9"/>
         <v>-1955422.2</v>
       </c>
       <c r="G593" t="str">
@@ -22818,7 +22801,7 @@
         <v>28715.200000000001</v>
       </c>
       <c r="F594" s="7">
-        <f>E594-D594</f>
+        <f t="shared" si="9"/>
         <v>-1769796.1</v>
       </c>
       <c r="G594" t="str">
@@ -22847,7 +22830,7 @@
         <v>29943.9</v>
       </c>
       <c r="F595" s="7">
-        <f>E595-D595</f>
+        <f t="shared" si="9"/>
         <v>-1888110.4000000001</v>
       </c>
       <c r="G595" t="str">
@@ -22876,7 +22859,7 @@
         <v>34078.300000000003</v>
       </c>
       <c r="F596" s="7">
-        <f>E596-D596</f>
+        <f t="shared" si="9"/>
         <v>-1721575.5</v>
       </c>
       <c r="G596" t="str">
@@ -22905,7 +22888,7 @@
         <v>1308.7</v>
       </c>
       <c r="F597" s="7">
-        <f>E597-D597</f>
+        <f t="shared" si="9"/>
         <v>-157224.79999999999</v>
       </c>
       <c r="G597" t="str">
@@ -22934,7 +22917,7 @@
         <v>1441.4</v>
       </c>
       <c r="F598" s="7">
-        <f>E598-D598</f>
+        <f t="shared" si="9"/>
         <v>-170825.80000000002</v>
       </c>
       <c r="G598" t="str">
@@ -22963,7 +22946,7 @@
         <v>1850.3</v>
       </c>
       <c r="F599" s="7">
-        <f>E599-D599</f>
+        <f t="shared" si="9"/>
         <v>-186807.40000000002</v>
       </c>
       <c r="G599" t="str">
@@ -22992,7 +22975,7 @@
         <v>1755.2</v>
       </c>
       <c r="F600" s="7">
-        <f>E600-D600</f>
+        <f t="shared" si="9"/>
         <v>-163369</v>
       </c>
       <c r="G600" t="str">
@@ -23021,7 +23004,7 @@
         <v>1055.7</v>
       </c>
       <c r="F601" s="7">
-        <f>E601-D601</f>
+        <f t="shared" si="9"/>
         <v>-153677.59999999998</v>
       </c>
       <c r="G601" t="str">
@@ -23050,7 +23033,7 @@
         <v>1256.3</v>
       </c>
       <c r="F602" s="7">
-        <f>E602-D602</f>
+        <f t="shared" si="9"/>
         <v>-193012</v>
       </c>
       <c r="G602" t="str">
@@ -23079,7 +23062,7 @@
         <v>1134.7</v>
       </c>
       <c r="F603" s="7">
-        <f>E603-D603</f>
+        <f t="shared" si="9"/>
         <v>-194198.09999999998</v>
       </c>
       <c r="G603" t="str">
@@ -23108,7 +23091,7 @@
         <v>1211</v>
       </c>
       <c r="F604" s="7">
-        <f>E604-D604</f>
+        <f t="shared" si="9"/>
         <v>-161898</v>
       </c>
       <c r="G604" t="str">
@@ -23137,7 +23120,7 @@
         <v>1861</v>
       </c>
       <c r="F605" s="7">
-        <f>E605-D605</f>
+        <f t="shared" si="9"/>
         <v>-207256.5</v>
       </c>
       <c r="G605" t="str">
@@ -23166,7 +23149,7 @@
         <v>1728.7</v>
       </c>
       <c r="F606" s="7">
-        <f>E606-D606</f>
+        <f t="shared" si="9"/>
         <v>-193578.19999999998</v>
       </c>
       <c r="G606" t="str">
@@ -23195,7 +23178,7 @@
         <v>5571.4</v>
       </c>
       <c r="F607" s="7">
-        <f>E607-D607</f>
+        <f t="shared" si="9"/>
         <v>-126953.5</v>
       </c>
       <c r="G607" t="str">
@@ -23224,7 +23207,7 @@
         <v>7037.8</v>
       </c>
       <c r="F608" s="7">
-        <f>E608-D608</f>
+        <f t="shared" si="9"/>
         <v>-125358.8</v>
       </c>
       <c r="G608" t="str">
@@ -23253,7 +23236,7 @@
         <v>6094.3</v>
       </c>
       <c r="F609" s="7">
-        <f>E609-D609</f>
+        <f t="shared" si="9"/>
         <v>-151398.1</v>
       </c>
       <c r="G609" t="str">
@@ -23282,7 +23265,7 @@
         <v>5550.8</v>
       </c>
       <c r="F610" s="7">
-        <f>E610-D610</f>
+        <f t="shared" si="9"/>
         <v>-177467.6</v>
       </c>
       <c r="G610" t="str">
@@ -23311,7 +23294,7 @@
         <v>5314.8</v>
       </c>
       <c r="F611" s="7">
-        <f>E611-D611</f>
+        <f t="shared" si="9"/>
         <v>-193550.90000000002</v>
       </c>
       <c r="G611" t="str">
@@ -23340,7 +23323,7 @@
         <v>10862.3</v>
       </c>
       <c r="F612" s="7">
-        <f>E612-D612</f>
+        <f t="shared" si="9"/>
         <v>-197987.6</v>
       </c>
       <c r="G612" t="str">
@@ -23369,7 +23352,7 @@
         <v>6528.7</v>
       </c>
       <c r="F613" s="7">
-        <f>E613-D613</f>
+        <f t="shared" si="9"/>
         <v>-168974.69999999998</v>
       </c>
       <c r="G613" t="str">
@@ -23398,7 +23381,7 @@
         <v>7141.5</v>
       </c>
       <c r="F614" s="7">
-        <f>E614-D614</f>
+        <f t="shared" si="9"/>
         <v>-153842.9</v>
       </c>
       <c r="G614" t="str">
@@ -23427,7 +23410,7 @@
         <v>7241.7</v>
       </c>
       <c r="F615" s="7">
-        <f>E615-D615</f>
+        <f t="shared" si="9"/>
         <v>-179443.4</v>
       </c>
       <c r="G615" t="str">
@@ -23456,7 +23439,7 @@
         <v>6657.6</v>
       </c>
       <c r="F616" s="7">
-        <f>E616-D616</f>
+        <f t="shared" si="9"/>
         <v>-187052.3</v>
       </c>
       <c r="G616" t="str">
@@ -23485,7 +23468,7 @@
         <v>10357</v>
       </c>
       <c r="F617" s="7">
-        <f>E617-D617</f>
+        <f t="shared" si="9"/>
         <v>-1341436.8</v>
       </c>
       <c r="G617" t="str">
@@ -23514,7 +23497,7 @@
         <v>11515.4</v>
       </c>
       <c r="F618" s="7">
-        <f>E618-D618</f>
+        <f t="shared" si="9"/>
         <v>-1378456.3</v>
       </c>
       <c r="G618" t="str">
@@ -23543,7 +23526,7 @@
         <v>9205.2999999999993</v>
       </c>
       <c r="F619" s="7">
-        <f>E619-D619</f>
+        <f t="shared" si="9"/>
         <v>-1372664.4</v>
       </c>
       <c r="G619" t="str">
@@ -23572,7 +23555,7 @@
         <v>11074.6</v>
       </c>
       <c r="F620" s="7">
-        <f>E620-D620</f>
+        <f t="shared" si="9"/>
         <v>-1348516.2</v>
       </c>
       <c r="G620" t="str">
@@ -23601,7 +23584,7 @@
         <v>9315.2999999999993</v>
       </c>
       <c r="F621" s="7">
-        <f>E621-D621</f>
+        <f t="shared" si="9"/>
         <v>-1339112.3999999999</v>
       </c>
       <c r="G621" t="str">
@@ -23630,7 +23613,7 @@
         <v>14562.9</v>
       </c>
       <c r="F622" s="7">
-        <f>E622-D622</f>
+        <f t="shared" si="9"/>
         <v>-1245608.4000000001</v>
       </c>
       <c r="G622" t="str">
@@ -23659,7 +23642,7 @@
         <v>11900.1</v>
       </c>
       <c r="F623" s="7">
-        <f>E623-D623</f>
+        <f t="shared" si="9"/>
         <v>-1064050.7</v>
       </c>
       <c r="G623" t="str">
@@ -23688,7 +23671,7 @@
         <v>10241.4</v>
       </c>
       <c r="F624" s="7">
-        <f>E624-D624</f>
+        <f t="shared" si="9"/>
         <v>-1046393.4999999999</v>
       </c>
       <c r="G624" t="str">
@@ -23717,7 +23700,7 @@
         <v>14563.3</v>
       </c>
       <c r="F625" s="7">
-        <f>E625-D625</f>
+        <f t="shared" si="9"/>
         <v>-1082218.5999999999</v>
       </c>
       <c r="G625" t="str">
@@ -23746,7 +23729,7 @@
         <v>11972.8</v>
       </c>
       <c r="F626" s="7">
-        <f>E626-D626</f>
+        <f t="shared" si="9"/>
         <v>-1016231.6</v>
       </c>
       <c r="G626" t="str">
@@ -23775,7 +23758,7 @@
         <v>7176</v>
       </c>
       <c r="F627" s="7">
-        <f>E627-D627</f>
+        <f t="shared" si="9"/>
         <v>-269947.59999999998</v>
       </c>
       <c r="G627" t="str">
@@ -23804,7 +23787,7 @@
         <v>6516.5</v>
       </c>
       <c r="F628" s="7">
-        <f>E628-D628</f>
+        <f t="shared" si="9"/>
         <v>-261622.3</v>
       </c>
       <c r="G628" t="str">
@@ -23833,7 +23816,7 @@
         <v>6809.2</v>
       </c>
       <c r="F629" s="7">
-        <f>E629-D629</f>
+        <f t="shared" si="9"/>
         <v>-269600.5</v>
       </c>
       <c r="G629" t="str">
@@ -23862,7 +23845,7 @@
         <v>6062.4</v>
       </c>
       <c r="F630" s="7">
-        <f>E630-D630</f>
+        <f t="shared" si="9"/>
         <v>-281361.5</v>
       </c>
       <c r="G630" t="str">
@@ -23891,7 +23874,7 @@
         <v>6891.7</v>
       </c>
       <c r="F631" s="7">
-        <f>E631-D631</f>
+        <f t="shared" si="9"/>
         <v>-300195.59999999998</v>
       </c>
       <c r="G631" t="str">
@@ -23920,7 +23903,7 @@
         <v>6500.2</v>
       </c>
       <c r="F632" s="7">
-        <f>E632-D632</f>
+        <f t="shared" si="9"/>
         <v>-270385.2</v>
       </c>
       <c r="G632" t="str">
@@ -23949,7 +23932,7 @@
         <v>4405</v>
       </c>
       <c r="F633" s="7">
-        <f>E633-D633</f>
+        <f t="shared" si="9"/>
         <v>-293101.7</v>
       </c>
       <c r="G633" t="str">
@@ -23978,7 +23961,7 @@
         <v>4335.3</v>
       </c>
       <c r="F634" s="7">
-        <f>E634-D634</f>
+        <f t="shared" si="9"/>
         <v>-280639.10000000003</v>
       </c>
       <c r="G634" t="str">
@@ -24007,7 +23990,7 @@
         <v>4855.3999999999996</v>
       </c>
       <c r="F635" s="7">
-        <f>E635-D635</f>
+        <f t="shared" si="9"/>
         <v>-276414</v>
       </c>
       <c r="G635" t="str">
@@ -24036,7 +24019,7 @@
         <v>3269</v>
       </c>
       <c r="F636" s="7">
-        <f>E636-D636</f>
+        <f t="shared" si="9"/>
         <v>-259485.90000000002</v>
       </c>
       <c r="G636" t="str">
@@ -24065,7 +24048,7 @@
         <v>124099.5</v>
       </c>
       <c r="F637" s="10">
-        <f>E637-D637</f>
+        <f t="shared" si="9"/>
         <v>-411425.5</v>
       </c>
       <c r="G637" t="str">
@@ -24094,7 +24077,7 @@
         <v>126457.4</v>
       </c>
       <c r="F638" s="10">
-        <f>E638-D638</f>
+        <f t="shared" si="9"/>
         <v>-387670</v>
       </c>
       <c r="G638" t="str">
@@ -24123,7 +24106,7 @@
         <v>123571.4</v>
       </c>
       <c r="F639" s="10">
-        <f>E639-D639</f>
+        <f t="shared" si="9"/>
         <v>-460809.1</v>
       </c>
       <c r="G639" t="str">
@@ -24152,7 +24135,7 @@
         <v>98872.5</v>
       </c>
       <c r="F640" s="10">
-        <f>E640-D640</f>
+        <f t="shared" si="9"/>
         <v>-368026.6</v>
       </c>
       <c r="G640" t="str">
@@ -24181,7 +24164,7 @@
         <v>87067.3</v>
       </c>
       <c r="F641" s="10">
-        <f>E641-D641</f>
+        <f t="shared" si="9"/>
         <v>-451891.50000000006</v>
       </c>
       <c r="G641" t="str">
@@ -24210,7 +24193,7 @@
         <v>33516.1</v>
       </c>
       <c r="F642" s="10">
-        <f>E642-D642</f>
+        <f t="shared" ref="F642:F705" si="10">E642-D642</f>
         <v>-496151.80000000005</v>
       </c>
       <c r="G642" t="str">
@@ -24239,7 +24222,7 @@
         <v>35769</v>
       </c>
       <c r="F643" s="10">
-        <f>E643-D643</f>
+        <f t="shared" si="10"/>
         <v>-519037.19999999995</v>
       </c>
       <c r="G643" t="str">
@@ -24268,7 +24251,7 @@
         <v>32915.4</v>
       </c>
       <c r="F644" s="10">
-        <f>E644-D644</f>
+        <f t="shared" si="10"/>
         <v>-650729.1</v>
       </c>
       <c r="G644" t="str">
@@ -24297,7 +24280,7 @@
         <v>38099.699999999997</v>
       </c>
       <c r="F645" s="10">
-        <f>E645-D645</f>
+        <f t="shared" si="10"/>
         <v>-593895</v>
       </c>
       <c r="G645" t="str">
@@ -24326,7 +24309,7 @@
         <v>77024.5</v>
       </c>
       <c r="F646" s="10">
-        <f>E646-D646</f>
+        <f t="shared" si="10"/>
         <v>-576739.80000000005</v>
       </c>
       <c r="G646" t="str">
@@ -24355,7 +24338,7 @@
         <v>17490.5</v>
       </c>
       <c r="F647" s="10">
-        <f>E647-D647</f>
+        <f t="shared" si="10"/>
         <v>17206.3</v>
       </c>
       <c r="G647" t="str">
@@ -24384,7 +24367,7 @@
         <v>17077.3</v>
       </c>
       <c r="F648" s="10">
-        <f>E648-D648</f>
+        <f t="shared" si="10"/>
         <v>16859.399999999998</v>
       </c>
       <c r="G648" t="str">
@@ -24413,7 +24396,7 @@
         <v>17732.599999999999</v>
       </c>
       <c r="F649" s="10">
-        <f>E649-D649</f>
+        <f t="shared" si="10"/>
         <v>17531.199999999997</v>
       </c>
       <c r="G649" t="str">
@@ -24442,7 +24425,7 @@
         <v>17693.599999999999</v>
       </c>
       <c r="F650" s="10">
-        <f>E650-D650</f>
+        <f t="shared" si="10"/>
         <v>16635.099999999999</v>
       </c>
       <c r="G650" t="str">
@@ -24471,7 +24454,7 @@
         <v>18948.7</v>
       </c>
       <c r="F651" s="10">
-        <f>E651-D651</f>
+        <f t="shared" si="10"/>
         <v>17938.3</v>
       </c>
       <c r="G651" t="str">
@@ -24500,7 +24483,7 @@
         <v>23708.7</v>
       </c>
       <c r="F652" s="10">
-        <f>E652-D652</f>
+        <f t="shared" si="10"/>
         <v>23306.799999999999</v>
       </c>
       <c r="G652" t="str">
@@ -24529,7 +24512,7 @@
         <v>21142.1</v>
       </c>
       <c r="F653" s="10">
-        <f>E653-D653</f>
+        <f t="shared" si="10"/>
         <v>20389.8</v>
       </c>
       <c r="G653" t="str">
@@ -24558,7 +24541,7 @@
         <v>21085.5</v>
       </c>
       <c r="F654" s="10">
-        <f>E654-D654</f>
+        <f t="shared" si="10"/>
         <v>20158.599999999999</v>
       </c>
       <c r="G654" t="str">
@@ -24587,7 +24570,7 @@
         <v>22031.200000000001</v>
       </c>
       <c r="F655" s="10">
-        <f>E655-D655</f>
+        <f t="shared" si="10"/>
         <v>20648</v>
       </c>
       <c r="G655" t="str">
@@ -24616,7 +24599,7 @@
         <v>20288.3</v>
       </c>
       <c r="F656" s="10">
-        <f>E656-D656</f>
+        <f t="shared" si="10"/>
         <v>18598.7</v>
       </c>
       <c r="G656" t="str">
@@ -24645,7 +24628,7 @@
         <v>10627.9</v>
       </c>
       <c r="F657" s="7">
-        <f>E657-D657</f>
+        <f t="shared" si="10"/>
         <v>-133011.9</v>
       </c>
       <c r="G657" t="str">
@@ -24674,7 +24657,7 @@
         <v>9786.4</v>
       </c>
       <c r="F658" s="7">
-        <f>E658-D658</f>
+        <f t="shared" si="10"/>
         <v>-116601.1</v>
       </c>
       <c r="G658" t="str">
@@ -24703,7 +24686,7 @@
         <v>8827.6</v>
       </c>
       <c r="F659" s="7">
-        <f>E659-D659</f>
+        <f t="shared" si="10"/>
         <v>-105365.9</v>
       </c>
       <c r="G659" t="str">
@@ -24732,7 +24715,7 @@
         <v>7040.7</v>
       </c>
       <c r="F660" s="7">
-        <f>E660-D660</f>
+        <f t="shared" si="10"/>
         <v>-120716.90000000001</v>
       </c>
       <c r="G660" t="str">
@@ -24761,7 +24744,7 @@
         <v>4618.6000000000004</v>
       </c>
       <c r="F661" s="7">
-        <f>E661-D661</f>
+        <f t="shared" si="10"/>
         <v>-126638.5</v>
       </c>
       <c r="G661" t="str">
@@ -24790,7 +24773,7 @@
         <v>5152.6000000000004</v>
       </c>
       <c r="F662" s="7">
-        <f>E662-D662</f>
+        <f t="shared" si="10"/>
         <v>-131147.9</v>
       </c>
       <c r="G662" t="str">
@@ -24819,7 +24802,7 @@
         <v>3828.5</v>
       </c>
       <c r="F663" s="7">
-        <f>E663-D663</f>
+        <f t="shared" si="10"/>
         <v>-115838.1</v>
       </c>
       <c r="G663" t="str">
@@ -24848,7 +24831,7 @@
         <v>3225.6</v>
       </c>
       <c r="F664" s="7">
-        <f>E664-D664</f>
+        <f t="shared" si="10"/>
         <v>-111584.29999999999</v>
       </c>
       <c r="G664" t="str">
@@ -24877,7 +24860,7 @@
         <v>5928.7</v>
       </c>
       <c r="F665" s="7">
-        <f>E665-D665</f>
+        <f t="shared" si="10"/>
         <v>-114859.7</v>
       </c>
       <c r="G665" t="str">
@@ -24906,7 +24889,7 @@
         <v>9260.1</v>
       </c>
       <c r="F666" s="7">
-        <f>E666-D666</f>
+        <f t="shared" si="10"/>
         <v>-86340</v>
       </c>
       <c r="G666" t="str">
@@ -24935,7 +24918,7 @@
         <v>24359.599999999999</v>
       </c>
       <c r="F667" s="10">
-        <f>E667-D667</f>
+        <f t="shared" si="10"/>
         <v>-306187</v>
       </c>
       <c r="G667" t="str">
@@ -24964,7 +24947,7 @@
         <v>61253.2</v>
       </c>
       <c r="F668" s="10">
-        <f>E668-D668</f>
+        <f t="shared" si="10"/>
         <v>-264584.89999999997</v>
       </c>
       <c r="G668" t="str">
@@ -24993,7 +24976,7 @@
         <v>61660.800000000003</v>
       </c>
       <c r="F669" s="10">
-        <f>E669-D669</f>
+        <f t="shared" si="10"/>
         <v>-266946.60000000003</v>
       </c>
       <c r="G669" t="str">
@@ -25022,7 +25005,7 @@
         <v>53557.2</v>
       </c>
       <c r="F670" s="10">
-        <f>E670-D670</f>
+        <f t="shared" si="10"/>
         <v>-345063.5</v>
       </c>
       <c r="G670" t="str">
@@ -25051,7 +25034,7 @@
         <v>35161.4</v>
       </c>
       <c r="F671" s="10">
-        <f>E671-D671</f>
+        <f t="shared" si="10"/>
         <v>-365723.19999999995</v>
       </c>
       <c r="G671" t="str">
@@ -25080,7 +25063,7 @@
         <v>29635.599999999999</v>
       </c>
       <c r="F672" s="10">
-        <f>E672-D672</f>
+        <f t="shared" si="10"/>
         <v>-394950.10000000003</v>
       </c>
       <c r="G672" t="str">
@@ -25109,7 +25092,7 @@
         <v>82813.8</v>
       </c>
       <c r="F673" s="7">
-        <f>E673-D673</f>
+        <f t="shared" si="10"/>
         <v>-509721.8</v>
       </c>
       <c r="G673" t="str">
@@ -25138,7 +25121,7 @@
         <v>78143.199999999997</v>
       </c>
       <c r="F674" s="7">
-        <f>E674-D674</f>
+        <f t="shared" si="10"/>
         <v>-514856.10000000003</v>
       </c>
       <c r="G674" t="str">
@@ -25167,7 +25150,7 @@
         <v>86752.1</v>
       </c>
       <c r="F675" s="7">
-        <f>E675-D675</f>
+        <f t="shared" si="10"/>
         <v>-510636.80000000005</v>
       </c>
       <c r="G675" t="str">
@@ -25196,7 +25179,7 @@
         <v>69644</v>
       </c>
       <c r="F676" s="7">
-        <f>E676-D676</f>
+        <f t="shared" si="10"/>
         <v>-563207.30000000005</v>
       </c>
       <c r="G676" t="str">
@@ -25225,7 +25208,7 @@
         <v>74702.5</v>
       </c>
       <c r="F677" s="7">
-        <f>E677-D677</f>
+        <f t="shared" si="10"/>
         <v>-643987.1</v>
       </c>
       <c r="G677" t="str">
@@ -25254,7 +25237,7 @@
         <v>73327.399999999994</v>
       </c>
       <c r="F678" s="7">
-        <f>E678-D678</f>
+        <f t="shared" si="10"/>
         <v>-623222.79999999993</v>
       </c>
       <c r="G678" t="str">
@@ -25283,7 +25266,7 @@
         <v>66408.7</v>
       </c>
       <c r="F679" s="7">
-        <f>E679-D679</f>
+        <f t="shared" si="10"/>
         <v>-570554.10000000009</v>
       </c>
       <c r="G679" t="str">
@@ -25312,7 +25295,7 @@
         <v>78761.100000000006</v>
       </c>
       <c r="F680" s="7">
-        <f>E680-D680</f>
+        <f t="shared" si="10"/>
         <v>-604939</v>
       </c>
       <c r="G680" t="str">
@@ -25341,7 +25324,7 @@
         <v>95754.1</v>
       </c>
       <c r="F681" s="7">
-        <f>E681-D681</f>
+        <f t="shared" si="10"/>
         <v>-597176.9</v>
       </c>
       <c r="G681" t="str">
@@ -25370,7 +25353,7 @@
         <v>95847.8</v>
       </c>
       <c r="F682" s="7">
-        <f>E682-D682</f>
+        <f t="shared" si="10"/>
         <v>-557602.6</v>
       </c>
       <c r="G682" t="str">
@@ -25399,7 +25382,7 @@
         <v>24093.9</v>
       </c>
       <c r="F683" s="7">
-        <f>E683-D683</f>
+        <f t="shared" si="10"/>
         <v>-52134.200000000004</v>
       </c>
       <c r="G683" t="str">
@@ -25428,7 +25411,7 @@
         <v>24679.3</v>
       </c>
       <c r="F684" s="7">
-        <f>E684-D684</f>
+        <f t="shared" si="10"/>
         <v>-61161.3</v>
       </c>
       <c r="G684" t="str">
@@ -25457,7 +25440,7 @@
         <v>25314.2</v>
       </c>
       <c r="F685" s="7">
-        <f>E685-D685</f>
+        <f t="shared" si="10"/>
         <v>-61034.7</v>
       </c>
       <c r="G685" t="str">
@@ -25486,7 +25469,7 @@
         <v>26843.1</v>
       </c>
       <c r="F686" s="7">
-        <f>E686-D686</f>
+        <f t="shared" si="10"/>
         <v>-59711.000000000007</v>
       </c>
       <c r="G686" t="str">
@@ -25515,7 +25498,7 @@
         <v>26521.4</v>
       </c>
       <c r="F687" s="7">
-        <f>E687-D687</f>
+        <f t="shared" si="10"/>
         <v>-51194.200000000004</v>
       </c>
       <c r="G687" t="str">
@@ -25544,7 +25527,7 @@
         <v>31971.5</v>
       </c>
       <c r="F688" s="7">
-        <f>E688-D688</f>
+        <f t="shared" si="10"/>
         <v>-53736.100000000006</v>
       </c>
       <c r="G688" t="str">
@@ -25573,7 +25556,7 @@
         <v>29082.3</v>
       </c>
       <c r="F689" s="7">
-        <f>E689-D689</f>
+        <f t="shared" si="10"/>
         <v>-51549.899999999994</v>
       </c>
       <c r="G689" t="str">
@@ -25602,7 +25585,7 @@
         <v>26876.799999999999</v>
       </c>
       <c r="F690" s="7">
-        <f>E690-D690</f>
+        <f t="shared" si="10"/>
         <v>-47432.2</v>
       </c>
       <c r="G690" t="str">
@@ -25631,7 +25614,7 @@
         <v>29261.5</v>
       </c>
       <c r="F691" s="7">
-        <f>E691-D691</f>
+        <f t="shared" si="10"/>
         <v>-43293.600000000006</v>
       </c>
       <c r="G691" t="str">
@@ -25660,7 +25643,7 @@
         <v>30132.3</v>
       </c>
       <c r="F692" s="7">
-        <f>E692-D692</f>
+        <f t="shared" si="10"/>
         <v>-39669.899999999994</v>
       </c>
       <c r="G692" t="str">
@@ -25689,7 +25672,7 @@
         <v>2301</v>
       </c>
       <c r="F693" s="10">
-        <f>E693-D693</f>
+        <f t="shared" si="10"/>
         <v>-116012.2</v>
       </c>
       <c r="G693" t="str">
@@ -25718,7 +25701,7 @@
         <v>2941.4</v>
       </c>
       <c r="F694" s="10">
-        <f>E694-D694</f>
+        <f t="shared" si="10"/>
         <v>-123144.6</v>
       </c>
       <c r="G694" t="str">
@@ -25747,7 +25730,7 @@
         <v>2254.6999999999998</v>
       </c>
       <c r="F695" s="10">
-        <f>E695-D695</f>
+        <f t="shared" si="10"/>
         <v>-131671.5</v>
       </c>
       <c r="G695" t="str">
@@ -25776,7 +25759,7 @@
         <v>2009.4</v>
       </c>
       <c r="F696" s="10">
-        <f>E696-D696</f>
+        <f t="shared" si="10"/>
         <v>-123927.20000000001</v>
       </c>
       <c r="G696" t="str">
@@ -25805,7 +25788,7 @@
         <v>2042.6</v>
       </c>
       <c r="F697" s="10">
-        <f>E697-D697</f>
+        <f t="shared" si="10"/>
         <v>-129094</v>
       </c>
       <c r="G697" t="str">
@@ -25834,7 +25817,7 @@
         <v>2605.1999999999998</v>
       </c>
       <c r="F698" s="10">
-        <f>E698-D698</f>
+        <f t="shared" si="10"/>
         <v>-131185.19999999998</v>
       </c>
       <c r="G698" t="str">
@@ -25863,7 +25846,7 @@
         <v>1817.9</v>
       </c>
       <c r="F699" s="10">
-        <f>E699-D699</f>
+        <f t="shared" si="10"/>
         <v>-118657.3</v>
       </c>
       <c r="G699" t="str">
@@ -25892,7 +25875,7 @@
         <v>2004.8</v>
       </c>
       <c r="F700" s="10">
-        <f>E700-D700</f>
+        <f t="shared" si="10"/>
         <v>-127313.9</v>
       </c>
       <c r="G700" t="str">
@@ -25921,7 +25904,7 @@
         <v>1725.4</v>
       </c>
       <c r="F701" s="10">
-        <f>E701-D701</f>
+        <f t="shared" si="10"/>
         <v>-124005.20000000001</v>
       </c>
       <c r="G701" t="str">
@@ -25950,7 +25933,7 @@
         <v>2037.5</v>
       </c>
       <c r="F702" s="10">
-        <f>E702-D702</f>
+        <f t="shared" si="10"/>
         <v>-133244.9</v>
       </c>
       <c r="G702" t="str">
@@ -25979,7 +25962,7 @@
         <v>1465</v>
       </c>
       <c r="F703" s="10">
-        <f>E703-D703</f>
+        <f t="shared" si="10"/>
         <v>1354.7</v>
       </c>
       <c r="G703" t="str">
@@ -26008,7 +25991,7 @@
         <v>1206.9000000000001</v>
       </c>
       <c r="F704" s="10">
-        <f>E704-D704</f>
+        <f t="shared" si="10"/>
         <v>1127.8000000000002</v>
       </c>
       <c r="G704" t="str">
@@ -26037,7 +26020,7 @@
         <v>1747.4</v>
       </c>
       <c r="F705" s="10">
-        <f>E705-D705</f>
+        <f t="shared" si="10"/>
         <v>1542.4</v>
       </c>
       <c r="G705" t="str">
@@ -26066,7 +26049,7 @@
         <v>1400</v>
       </c>
       <c r="F706" s="10">
-        <f>E706-D706</f>
+        <f t="shared" ref="F706:F769" si="11">E706-D706</f>
         <v>1282.3</v>
       </c>
       <c r="G706" t="str">
@@ -26079,291 +26062,291 @@
       </c>
     </row>
     <row r="707" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A707" s="17">
+      <c r="A707" s="5">
         <v>2016</v>
       </c>
-      <c r="B707" s="17">
+      <c r="B707" s="5">
         <v>4002319000</v>
       </c>
-      <c r="C707" s="24" t="s">
+      <c r="C707" s="16" t="s">
         <v>414</v>
       </c>
-      <c r="D707" s="18">
+      <c r="D707" s="6">
         <v>406.6</v>
       </c>
-      <c r="E707" s="18">
+      <c r="E707" s="6">
         <v>15706.5</v>
       </c>
-      <c r="F707" s="21">
-        <f t="shared" ref="F707:F716" si="0">E707-D707</f>
+      <c r="F707" s="10">
+        <f t="shared" ref="F707:F716" si="12">E707-D707</f>
         <v>15299.9</v>
       </c>
-      <c r="G707" s="22" t="str">
-        <f>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</f>
-        <v>import</v>
-      </c>
-      <c r="H707" s="23">
+      <c r="G707" t="str">
+        <f>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</f>
+        <v>import</v>
+      </c>
+      <c r="H707" s="15">
         <f>ABS(표1[[#This Row],[export]]-표1[[#This Row],[import]])/(표1[[#This Row],[export]]+표1[[#This Row],[import]])</f>
         <v>0.94953174746014113</v>
       </c>
     </row>
     <row r="708" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A708" s="17">
+      <c r="A708" s="5">
         <v>2017</v>
       </c>
-      <c r="B708" s="17">
+      <c r="B708" s="5">
         <v>4002319000</v>
       </c>
-      <c r="C708" s="24" t="s">
+      <c r="C708" s="16" t="s">
         <v>414</v>
       </c>
-      <c r="D708" s="18">
+      <c r="D708" s="6">
         <v>423.1</v>
       </c>
-      <c r="E708" s="18">
+      <c r="E708" s="6">
         <v>16181.7</v>
       </c>
-      <c r="F708" s="21">
-        <f t="shared" si="0"/>
+      <c r="F708" s="10">
+        <f t="shared" si="12"/>
         <v>15758.6</v>
       </c>
-      <c r="G708" s="22" t="str">
-        <f>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</f>
-        <v>import</v>
-      </c>
-      <c r="H708" s="23">
+      <c r="G708" t="str">
+        <f>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</f>
+        <v>import</v>
+      </c>
+      <c r="H708" s="15">
         <f>ABS(표1[[#This Row],[export]]-표1[[#This Row],[import]])/(표1[[#This Row],[export]]+표1[[#This Row],[import]])</f>
         <v>0.94903883214492202</v>
       </c>
     </row>
     <row r="709" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A709" s="17">
+      <c r="A709" s="5">
         <v>2018</v>
       </c>
-      <c r="B709" s="17">
+      <c r="B709" s="5">
         <v>4002319000</v>
       </c>
-      <c r="C709" s="24" t="s">
+      <c r="C709" s="16" t="s">
         <v>414</v>
       </c>
-      <c r="D709" s="18">
+      <c r="D709" s="6">
         <v>280.7</v>
       </c>
-      <c r="E709" s="18">
+      <c r="E709" s="6">
         <v>13302.8</v>
       </c>
-      <c r="F709" s="21">
-        <f t="shared" si="0"/>
+      <c r="F709" s="10">
+        <f t="shared" si="12"/>
         <v>13022.099999999999</v>
       </c>
-      <c r="G709" s="22" t="str">
-        <f>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</f>
-        <v>import</v>
-      </c>
-      <c r="H709" s="23">
+      <c r="G709" t="str">
+        <f>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</f>
+        <v>import</v>
+      </c>
+      <c r="H709" s="15">
         <f>ABS(표1[[#This Row],[export]]-표1[[#This Row],[import]])/(표1[[#This Row],[export]]+표1[[#This Row],[import]])</f>
         <v>0.95867044576140159</v>
       </c>
     </row>
     <row r="710" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A710" s="17">
+      <c r="A710" s="5">
         <v>2019</v>
       </c>
-      <c r="B710" s="17">
+      <c r="B710" s="5">
         <v>4002319000</v>
       </c>
-      <c r="C710" s="24" t="s">
+      <c r="C710" s="16" t="s">
         <v>414</v>
       </c>
-      <c r="D710" s="18">
+      <c r="D710" s="6">
         <v>619.6</v>
       </c>
-      <c r="E710" s="18">
+      <c r="E710" s="6">
         <v>12039.9</v>
       </c>
-      <c r="F710" s="21">
-        <f t="shared" si="0"/>
+      <c r="F710" s="10">
+        <f t="shared" si="12"/>
         <v>11420.3</v>
       </c>
-      <c r="G710" s="22" t="str">
-        <f>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</f>
-        <v>import</v>
-      </c>
-      <c r="H710" s="23">
+      <c r="G710" t="str">
+        <f>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</f>
+        <v>import</v>
+      </c>
+      <c r="H710" s="15">
         <f>ABS(표1[[#This Row],[export]]-표1[[#This Row],[import]])/(표1[[#This Row],[export]]+표1[[#This Row],[import]])</f>
         <v>0.90211303763971717</v>
       </c>
     </row>
     <row r="711" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A711" s="17">
+      <c r="A711" s="5">
         <v>2020</v>
       </c>
-      <c r="B711" s="17">
+      <c r="B711" s="5">
         <v>4002319000</v>
       </c>
-      <c r="C711" s="24" t="s">
+      <c r="C711" s="16" t="s">
         <v>414</v>
       </c>
-      <c r="D711" s="18">
+      <c r="D711" s="6">
         <v>446.9</v>
       </c>
-      <c r="E711" s="18">
+      <c r="E711" s="6">
         <v>11050.5</v>
       </c>
-      <c r="F711" s="21">
-        <f t="shared" si="0"/>
+      <c r="F711" s="10">
+        <f t="shared" si="12"/>
         <v>10603.6</v>
       </c>
-      <c r="G711" s="22" t="str">
-        <f>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</f>
-        <v>import</v>
-      </c>
-      <c r="H711" s="23">
+      <c r="G711" t="str">
+        <f>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</f>
+        <v>import</v>
+      </c>
+      <c r="H711" s="15">
         <f>ABS(표1[[#This Row],[export]]-표1[[#This Row],[import]])/(표1[[#This Row],[export]]+표1[[#This Row],[import]])</f>
         <v>0.92226068502444036</v>
       </c>
     </row>
     <row r="712" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A712" s="17">
+      <c r="A712" s="5">
         <v>2021</v>
       </c>
-      <c r="B712" s="17">
+      <c r="B712" s="5">
         <v>4002319000</v>
       </c>
-      <c r="C712" s="24" t="s">
+      <c r="C712" s="16" t="s">
         <v>414</v>
       </c>
-      <c r="D712" s="18">
+      <c r="D712" s="6">
         <v>247.1</v>
       </c>
-      <c r="E712" s="18">
+      <c r="E712" s="6">
         <v>14574.5</v>
       </c>
-      <c r="F712" s="21">
-        <f t="shared" si="0"/>
+      <c r="F712" s="10">
+        <f t="shared" si="12"/>
         <v>14327.4</v>
       </c>
-      <c r="G712" s="22" t="str">
-        <f>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</f>
-        <v>import</v>
-      </c>
-      <c r="H712" s="23">
+      <c r="G712" t="str">
+        <f>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</f>
+        <v>import</v>
+      </c>
+      <c r="H712" s="15">
         <f>ABS(표1[[#This Row],[export]]-표1[[#This Row],[import]])/(표1[[#This Row],[export]]+표1[[#This Row],[import]])</f>
         <v>0.9666567711987909</v>
       </c>
     </row>
     <row r="713" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A713" s="17">
+      <c r="A713" s="5">
         <v>2022</v>
       </c>
-      <c r="B713" s="17">
+      <c r="B713" s="5">
         <v>4002319000</v>
       </c>
-      <c r="C713" s="24" t="s">
+      <c r="C713" s="16" t="s">
         <v>414</v>
       </c>
-      <c r="D713" s="18">
+      <c r="D713" s="6">
         <v>545.4</v>
       </c>
-      <c r="E713" s="18">
+      <c r="E713" s="6">
         <v>12539.8</v>
       </c>
-      <c r="F713" s="21">
-        <f t="shared" si="0"/>
+      <c r="F713" s="10">
+        <f t="shared" si="12"/>
         <v>11994.4</v>
       </c>
-      <c r="G713" s="22" t="str">
-        <f>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</f>
-        <v>import</v>
-      </c>
-      <c r="H713" s="23">
+      <c r="G713" t="str">
+        <f>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</f>
+        <v>import</v>
+      </c>
+      <c r="H713" s="15">
         <f>ABS(표1[[#This Row],[export]]-표1[[#This Row],[import]])/(표1[[#This Row],[export]]+표1[[#This Row],[import]])</f>
         <v>0.91663864518692884</v>
       </c>
     </row>
     <row r="714" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A714" s="17">
+      <c r="A714" s="5">
         <v>2023</v>
       </c>
-      <c r="B714" s="17">
+      <c r="B714" s="5">
         <v>4002319000</v>
       </c>
-      <c r="C714" s="24" t="s">
+      <c r="C714" s="16" t="s">
         <v>414</v>
       </c>
-      <c r="D714" s="18">
+      <c r="D714" s="6">
         <v>524.29999999999995</v>
       </c>
-      <c r="E714" s="18">
+      <c r="E714" s="6">
         <v>8659.1</v>
       </c>
-      <c r="F714" s="21">
-        <f t="shared" si="0"/>
+      <c r="F714" s="10">
+        <f t="shared" si="12"/>
         <v>8134.8</v>
       </c>
-      <c r="G714" s="22" t="str">
-        <f>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</f>
-        <v>import</v>
-      </c>
-      <c r="H714" s="23">
+      <c r="G714" t="str">
+        <f>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</f>
+        <v>import</v>
+      </c>
+      <c r="H714" s="15">
         <f>ABS(표1[[#This Row],[export]]-표1[[#This Row],[import]])/(표1[[#This Row],[export]]+표1[[#This Row],[import]])</f>
         <v>0.88581571095672629</v>
       </c>
     </row>
     <row r="715" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A715" s="17">
+      <c r="A715" s="5">
         <v>2024</v>
       </c>
-      <c r="B715" s="17">
+      <c r="B715" s="5">
         <v>4002319000</v>
       </c>
-      <c r="C715" s="24" t="s">
+      <c r="C715" s="16" t="s">
         <v>414</v>
       </c>
-      <c r="D715" s="18">
+      <c r="D715" s="6">
         <v>280.89999999999998</v>
       </c>
-      <c r="E715" s="18">
+      <c r="E715" s="6">
         <v>9073.6</v>
       </c>
-      <c r="F715" s="21">
-        <f t="shared" si="0"/>
+      <c r="F715" s="10">
+        <f t="shared" si="12"/>
         <v>8792.7000000000007</v>
       </c>
-      <c r="G715" s="22" t="str">
-        <f>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</f>
-        <v>import</v>
-      </c>
-      <c r="H715" s="23">
+      <c r="G715" t="str">
+        <f>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</f>
+        <v>import</v>
+      </c>
+      <c r="H715" s="15">
         <f>ABS(표1[[#This Row],[export]]-표1[[#This Row],[import]])/(표1[[#This Row],[export]]+표1[[#This Row],[import]])</f>
         <v>0.93994334277620406</v>
       </c>
     </row>
     <row r="716" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A716" s="19">
+      <c r="A716" s="11">
         <v>2025</v>
       </c>
-      <c r="B716" s="19">
+      <c r="B716" s="11">
         <v>4002319000</v>
       </c>
-      <c r="C716" s="24" t="s">
+      <c r="C716" s="16" t="s">
         <v>414</v>
       </c>
-      <c r="D716" s="20">
+      <c r="D716" s="12">
         <v>178.5</v>
       </c>
-      <c r="E716" s="20">
+      <c r="E716" s="12">
         <v>8239.4</v>
       </c>
-      <c r="F716" s="21">
-        <f t="shared" si="0"/>
+      <c r="F716" s="10">
+        <f t="shared" si="12"/>
         <v>8060.9</v>
       </c>
-      <c r="G716" s="22" t="str">
-        <f>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</f>
-        <v>import</v>
-      </c>
-      <c r="H716" s="23">
+      <c r="G716" t="str">
+        <f>IF(표1[[#This Row],[diff]]&gt;0,"import","export")</f>
+        <v>import</v>
+      </c>
+      <c r="H716" s="15">
         <f>ABS(표1[[#This Row],[export]]-표1[[#This Row],[import]])/(표1[[#This Row],[export]]+표1[[#This Row],[import]])</f>
         <v>0.95759037289585291</v>
       </c>
